--- a/data/S1994_95_FINAL.xlsx
+++ b/data/S1994_95_FINAL.xlsx
@@ -24,8 +24,11 @@
     <sheet name="SERIES" sheetId="15" state="visible" r:id="rId15"/>
     <sheet name="CLUBS" sheetId="16" state="visible" r:id="rId16"/>
     <sheet name="META" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="TODO" sheetId="18" state="visible" r:id="rId18"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'TODO'!$A$1:$F$21</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -33,7 +36,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -48,8 +51,12 @@
       <name val="Arial"/>
       <b val="1"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -71,6 +78,11 @@
         <fgColor rgb="00F2F2F2"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00305496"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -84,12 +96,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -15010,7 +15028,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15054,6 +15072,266 @@
       <c r="D2" t="inlineStr">
         <is>
           <t>DS-PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id: CLUB_S1994_95_0262 'Hrušky B' prev→CLUB_S1993_94_0340 jen dle jména (město liší) — ověřit (D24)</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>[TBD] fate: CLUB_S1994_95_0027 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>[TBD] fate: CLUB_S1994_95_0029 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>[TBD] fate: CLUB_S1994_95_0030 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>[TBD] fate: CLUB_S1994_95_0117 fate nekonzist. ['postup', 'reorganizace'] → 'reorganizace' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>[TBD] fate: CLUB_S1994_95_0118 fate nekonzist. ['postup', 'reorganizace'] → 'reorganizace' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>[TBD] fate: CLUB_S1994_95_0119 fate nekonzist. ['postup', 'reorganizace'] → 'reorganizace' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>[TBD] fate: CLUB_S1994_95_0120 fate nekonzist. ['postup', 'reorganizace'] → 'reorganizace' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>[TBD] fate: CLUB_S1994_95_0121 fate nekonzist. ['postup', 'reorganizace'] → 'reorganizace' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>[TBD] fate: CLUB_S1994_95_0159 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>[TBD] fate: CLUB_S1994_95_0162 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>[TBD] fate: CLUB_S1994_95_0186 fate nekonzist. ['reorganizace', 'setrval'] → 'reorganizace' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>[TBD] fate: CLUB_S1994_95_0187 fate nekonzist. ['reorganizace', 'setrval'] → 'reorganizace' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>[TBD] fate: CLUB_S1994_95_0188 fate nekonzist. ['reorganizace', 'setrval'] → 'reorganizace' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>[TBD] fate: CLUB_S1994_95_0189 fate nekonzist. ['reorganizace', 'setrval'] → 'reorganizace' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>[TBD] fate: CLUB_S1994_95_0191 fate nekonzist. ['reorganizace', 'setrval'] → 'reorganizace' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>NODE_S1994_95_0020</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida: SYSTEM NODE_S1994_95_0020 'Baráž o Extraligu' (L15, parent=NODE_S1994_95_0001) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>NODE_S1994_95_0026</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida: SYSTEM NODE_S1994_95_0026 'Baráž o 1.ligu' (L25, parent=NODE_S1994_95_0003) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>NODE_S1994_95_0027</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida: SYSTEM NODE_S1994_95_0027 'Kvalifikace o 2.ligu' (L25, parent=NODE_S1994_95_0031) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>NODE_S1994_95_0035</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida: SYSTEM NODE_S1994_95_0035 'Baráž o 1.ligu (vazba z II.ligy)' (L25, parent=NODE_S1994_95_0031) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
         </is>
       </c>
     </row>
@@ -18790,8 +19068,6 @@
         </is>
       </c>
     </row>
-    <row r="88"/>
-    <row r="89"/>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
@@ -18871,7 +19147,6 @@
         </is>
       </c>
     </row>
-    <row r="97"/>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
@@ -35074,6 +35349,501 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="88" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>typ</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="D1" s="5" t="inlineStr">
+        <is>
+          <t>popis</t>
+        </is>
+      </c>
+      <c r="E1" s="5" t="inlineStr">
+        <is>
+          <t>vyřešeno? (ANO/ne)</t>
+        </is>
+      </c>
+      <c r="F1" s="5" t="inlineStr">
+        <is>
+          <t>poznámka kolegy</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>prev_club_id</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0262</t>
+        </is>
+      </c>
+      <c r="D2" s="6" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0262 'Hrušky B' prev→CLUB_S1993_94_0340 jen dle jména (město liší) — ověřit (D24)</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>fate</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0027</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0027 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>fate</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0029</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0029 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>fate</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0030</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0030 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>fate</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0117</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0117 fate nekonzist. ['postup', 'reorganizace'] → 'reorganizace' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>fate</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0118</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0118 fate nekonzist. ['postup', 'reorganizace'] → 'reorganizace' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>fate</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0119</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0119 fate nekonzist. ['postup', 'reorganizace'] → 'reorganizace' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>fate</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0120</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0120 fate nekonzist. ['postup', 'reorganizace'] → 'reorganizace' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>fate</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0121</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0121 fate nekonzist. ['postup', 'reorganizace'] → 'reorganizace' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>fate</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0159</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0159 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>fate</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0162</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0162 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>fate</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0186</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0186 fate nekonzist. ['reorganizace', 'setrval'] → 'reorganizace' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>fate</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0187</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0187 fate nekonzist. ['reorganizace', 'setrval'] → 'reorganizace' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>fate</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0188</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0188 fate nekonzist. ['reorganizace', 'setrval'] → 'reorganizace' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>fate</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0189</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0189 fate nekonzist. ['reorganizace', 'setrval'] → 'reorganizace' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>fate</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0191</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0191 fate nekonzist. ['reorganizace', 'setrval'] → 'reorganizace' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>pyramida</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NODE_S1994_95_0020</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>SYSTEM NODE_S1994_95_0020 'Baráž o Extraligu' (L15, parent=NODE_S1994_95_0001) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>pyramida</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NODE_S1994_95_0026</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>SYSTEM NODE_S1994_95_0026 'Baráž o 1.ligu' (L25, parent=NODE_S1994_95_0003) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>pyramida</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NODE_S1994_95_0027</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>SYSTEM NODE_S1994_95_0027 'Kvalifikace o 2.ligu' (L25, parent=NODE_S1994_95_0031) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>pyramida</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NODE_S1994_95_0035</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>SYSTEM NODE_S1994_95_0035 'Baráž o 1.ligu (vazba z II.ligy)' (L25, parent=NODE_S1994_95_0031) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:F21"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/data/S1994_95_FINAL.xlsx
+++ b/data/S1994_95_FINAL.xlsx
@@ -27,7 +27,7 @@
     <sheet name="TODO" sheetId="18" state="visible" r:id="rId18"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'TODO'!$A$1:$F$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'TODO'!$A$1:$F$36</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -15028,7 +15028,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:D37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15078,7 +15078,7 @@
     <row r="3">
       <c r="C3" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id: CLUB_S1994_95_0262 'Hrušky B' prev→CLUB_S1993_94_0340 jen dle jména (město liší) — ověřit (D24)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -15090,7 +15090,7 @@
     <row r="4">
       <c r="C4" t="inlineStr">
         <is>
-          <t>[TBD] fate: CLUB_S1994_95_0027 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -15102,7 +15102,7 @@
     <row r="5">
       <c r="C5" t="inlineStr">
         <is>
-          <t>[TBD] fate: CLUB_S1994_95_0029 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -15114,7 +15114,7 @@
     <row r="6">
       <c r="C6" t="inlineStr">
         <is>
-          <t>[TBD] fate: CLUB_S1994_95_0030 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'České Budějovice' → 'Slezan Opava' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -15126,7 +15126,7 @@
     <row r="7">
       <c r="C7" t="inlineStr">
         <is>
-          <t>[TBD] fate: CLUB_S1994_95_0117 fate nekonzist. ['postup', 'reorganizace'] → 'reorganizace' (cross-ref=ano) — ověřit</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -15138,7 +15138,7 @@
     <row r="8">
       <c r="C8" t="inlineStr">
         <is>
-          <t>[TBD] fate: CLUB_S1994_95_0118 fate nekonzist. ['postup', 'reorganizace'] → 'reorganizace' (cross-ref=ano) — ověřit</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -15150,7 +15150,7 @@
     <row r="9">
       <c r="C9" t="inlineStr">
         <is>
-          <t>[TBD] fate: CLUB_S1994_95_0119 fate nekonzist. ['postup', 'reorganizace'] → 'reorganizace' (cross-ref=ano) — ověřit</t>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -15162,7 +15162,7 @@
     <row r="10">
       <c r="C10" t="inlineStr">
         <is>
-          <t>[TBD] fate: CLUB_S1994_95_0120 fate nekonzist. ['postup', 'reorganizace'] → 'reorganizace' (cross-ref=ano) — ověřit</t>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -15174,7 +15174,7 @@
     <row r="11">
       <c r="C11" t="inlineStr">
         <is>
-          <t>[TBD] fate: CLUB_S1994_95_0121 fate nekonzist. ['postup', 'reorganizace'] → 'reorganizace' (cross-ref=ano) — ověřit</t>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -15186,7 +15186,7 @@
     <row r="12">
       <c r="C12" t="inlineStr">
         <is>
-          <t>[TBD] fate: CLUB_S1994_95_0159 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -15198,7 +15198,7 @@
     <row r="13">
       <c r="C13" t="inlineStr">
         <is>
-          <t>[TBD] fate: CLUB_S1994_95_0162 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'KLH VT VTJ Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -15210,7 +15210,7 @@
     <row r="14">
       <c r="C14" t="inlineStr">
         <is>
-          <t>[TBD] fate: CLUB_S1994_95_0186 fate nekonzist. ['reorganizace', 'setrval'] → 'reorganizace' (cross-ref=ano) — ověřit</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Prostějov' → 'Mariánské Lázně' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -15222,7 +15222,7 @@
     <row r="15">
       <c r="C15" t="inlineStr">
         <is>
-          <t>[TBD] fate: CLUB_S1994_95_0187 fate nekonzist. ['reorganizace', 'setrval'] → 'reorganizace' (cross-ref=ano) — ověřit</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -15234,7 +15234,7 @@
     <row r="16">
       <c r="C16" t="inlineStr">
         <is>
-          <t>[TBD] fate: CLUB_S1994_95_0188 fate nekonzist. ['reorganizace', 'setrval'] → 'reorganizace' (cross-ref=ano) — ověřit</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1993_94_0096 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -15246,7 +15246,7 @@
     <row r="17">
       <c r="C17" t="inlineStr">
         <is>
-          <t>[TBD] fate: CLUB_S1994_95_0189 fate nekonzist. ['reorganizace', 'setrval'] → 'reorganizace' (cross-ref=ano) — ověřit</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1993_94_0124 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -15258,7 +15258,7 @@
     <row r="18">
       <c r="C18" t="inlineStr">
         <is>
-          <t>[TBD] fate: CLUB_S1994_95_0191 fate nekonzist. ['reorganizace', 'setrval'] → 'reorganizace' (cross-ref=ano) — ověřit</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -15268,14 +15268,9 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>NODE_S1994_95_0020</t>
-        </is>
-      </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>[TBD] pyramida: SYSTEM NODE_S1994_95_0020 'Baráž o Extraligu' (L15, parent=NODE_S1994_95_0001) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -15285,14 +15280,9 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>NODE_S1994_95_0026</t>
-        </is>
-      </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>[TBD] pyramida: SYSTEM NODE_S1994_95_0026 'Baráž o 1.ligu' (L25, parent=NODE_S1994_95_0003) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -15302,14 +15292,9 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>NODE_S1994_95_0027</t>
-        </is>
-      </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>[TBD] pyramida: SYSTEM NODE_S1994_95_0027 'Kvalifikace o 2.ligu' (L25, parent=NODE_S1994_95_0031) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -15319,17 +15304,192 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>NODE_S1994_95_0035</t>
-        </is>
-      </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>[TBD] pyramida: SYSTEM NODE_S1994_95_0035 'Baráž o 1.ligu (vazba z II.ligy)' (L25, parent=NODE_S1994_95_0031) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Bižuterie Jablonec' → 'Jablonec nad Nisou' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Stadion Nový Bydžov' → 'Nový Bydžov' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: K ověření, zda jde o B-tým nebo samostatný klub (Česká Třebová mohla mít dva různé kluby). Smart fix prev: 0650 (Sokol Česká Třebová = jiný klub) → 0656 (Perla II z 49/50 = B-tým Perly). Audit 04/2026.</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: clean = "(Třešť) – (Dačice)" - format meziokresni soutez nejasny. K vyjasneni Pavlem (D40). Almanach komentar ponechan.</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1993_94_0340 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1993_94_0358 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
         <is>
           <t>TODO-auto</t>
         </is>
@@ -19068,6 +19228,8 @@
         </is>
       </c>
     </row>
+    <row r="88"/>
+    <row r="89"/>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
@@ -19098,6 +19260,11 @@
           <t>I.ČNHL (12 CZ) + SNHL (12 SVK)</t>
         </is>
       </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>NODE_S1994_95_0001</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -19110,6 +19277,11 @@
           <t>Kvalifikace o II.ligu</t>
         </is>
       </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>NODE_S1994_95_0003</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -19122,6 +19294,11 @@
           <t>Krajské přebory (nové velké kraje!)</t>
         </is>
       </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>NODE_S1994_95_0003</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -19134,6 +19311,11 @@
           <t>I.třída / I.B třída / Krajská soutěž</t>
         </is>
       </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>NODE_S1994_95_0031</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -19147,6 +19329,7 @@
         </is>
       </c>
     </row>
+    <row r="97"/>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
@@ -21603,12 +21786,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Plzeň</t>
+          <t>České Budějovice</t>
         </is>
       </c>
     </row>
@@ -21944,12 +22127,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Třinec = TJ TŽ VŘSR Třinec (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj. **TŽ** = Třinecké železárny. **VŘSR** = Velka řijnova socialisticka revoluce (pojmenovani po vyroci VŘSR 1917). city Třinec.</t>
+          <t>Třinec = TJ TŽ VŘSR Třinec (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj. **TŽ** = Třinecké železárny. **VŘSR** = Velka řijnova socialisticka revoluce (pojmenovani po vyroci VŘSR 1917). city Třinec. || TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>TŽ VŘSR Třinec</t>
+          <t>Třinec</t>
         </is>
       </c>
     </row>
@@ -21991,12 +22174,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Slovan JH = HC Vajgar/Strelci JH (Wiki D42 - registr ustavy 04/2026). Chain VBK Vajgar (1929). NE Hradec Kralove. city Jindřichův Hradec.</t>
+          <t>Slovan JH = HC Vajgar/Strelci JH (Wiki D42 - registr ustavy 04/2026). Chain VBK Vajgar (1929). NE Hradec Kralove. city Jindřichův Hradec. || TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Vajgar Jindřichův Hradec</t>
+          <t>Jindřichův Hradec</t>
         </is>
       </c>
     </row>
@@ -22159,12 +22342,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Slavoj České Budějovice B (Wiki D42 - registr ustavy 04/2026). B-tym hlavni Motor CB chain. city České Budějovice.</t>
+          <t>Slavoj České Budějovice B (Wiki D42 - registr ustavy 04/2026). B-tym hlavni Motor CB chain. city České Budějovice. || TBD: city 'České Budějovice' → 'Slezan Opava' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Slezan Opava</t>
         </is>
       </c>
     </row>
@@ -22206,12 +22389,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov.</t>
+          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov. || TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
     </row>
@@ -22248,12 +22431,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Ústí nad Labem = TJ Slovan NV Ústí nL Labem (Wiki D42 - registr ustavy 04/2026). **NV** = Národní výbor (správní orgán). city Ústí nad Labem.</t>
+          <t>Ústí nad Labem = TJ Slovan NV Ústí nL Labem (Wiki D42 - registr ustavy 04/2026). **NV** = Národní výbor (správní orgán). city Ústí nad Labem. || TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>NV Ústí nad Labem</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
     </row>
@@ -22708,14 +22891,9 @@
           <t>L40</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>CLUB_S1993_94_0005</t>
-        </is>
-      </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Identity transition VERIFIKOVÁNA Wikipedií (D18) — genealogie: ZMP Praha → Sokol Šverma Jinonice → Spartak Motorlet Praha. Almanach 51/52 zachycuje fázi „Sokol Šverma Jinonice" s odkazem na předchůdce ZSJ ZMP Praha. (TBD odstraněn 04/2026.) || Šverma Jinonice (ZSJ ZMP Praha) 51/52 (10_liga, postup do 1.ligy). I. ČLTK Praha (Wiki D18 / D42). Genealogie: I. ČLTK Praha (1923, Český Lawn-tenisový klub) -&gt; Sokol ZMP Praha (1948) -&gt; ZSJ ZMP Praha (1949) -&gt; ZSJ Sokol Šverma Jinonice (1951) -&gt; DSO Spartak Motorlet Praha (1953) -&gt; TJ Spartak Motorlet Praha (1957) -&gt; TJ ČLTK Motorlet Praha (1969) -&gt; TJ DP I. ČLTK Praha (1970) -&gt; I. ČLTK Praha (1992). Motorlet = zavod ve čtvrti Jinonice (Praha 5). city Praha. || Praha = vsechny prazske kluby (Wiki D42 - registr ustavy 04/2026). VELKA metropole, VICE rovnocennych chains (D45 TYP 1). HLAVNI: (1) HC Sparta Praha (1903-) - dnes Tipsport ELH. (2) HC Slavia Praha (1900) - dnes 1.liga. (3) Skoda Plzen sice ne, ale prazsky paralelni: HC Kobra Praha. Mestske casti: Vokovice, Aritma, Strešovice, Strašnice, Tesla, Vyšehrad, Motol, Hostivař, Kobylisy, Vinohrady, Podolí, Dejvice, Holešovice, Vršovice, Bohnice, Karlín, Smíchov, Žižkov, Nuseľ, Libeň, Vysočany. Stalingrad = mestska cast Prahy 7 (1949-1962, dnes Holešovice). Železničáři Praha = paralelni Lokomotiva chain. city Praha.</t>
+          <t>Identity transition VERIFIKOVÁNA Wikipedií (D18) — genealogie: ZMP Praha → Sokol Šverma Jinonice → Spartak Motorlet Praha. Almanach 51/52 zachycuje fázi „Sokol Šverma Jinonice" s odkazem na předchůdce ZSJ ZMP Praha. (TBD odstraněn 04/2026.) || Šverma Jinonice (ZSJ ZMP Praha) 51/52 (10_liga, postup do 1.ligy). I. ČLTK Praha (Wiki D18 / D42). Genealogie: I. ČLTK Praha (1923, Český Lawn-tenisový klub) -&gt; Sokol ZMP Praha (1948) -&gt; ZSJ ZMP Praha (1949) -&gt; ZSJ Sokol Šverma Jinonice (1951) -&gt; DSO Spartak Motorlet Praha (1953) -&gt; TJ Spartak Motorlet Praha (1957) -&gt; TJ ČLTK Motorlet Praha (1969) -&gt; TJ DP I. ČLTK Praha (1970) -&gt; I. ČLTK Praha (1992). Motorlet = zavod ve čtvrti Jinonice (Praha 5). city Praha. || Praha = vsechny prazske kluby (Wiki D42 - registr ustavy 04/2026). VELKA metropole, VICE rovnocennych chains (D45 TYP 1). HLAVNI: (1) HC Sparta Praha (1903-) - dnes Tipsport ELH. (2) HC Slavia Praha (1900) - dnes 1.liga. (3) Skoda Plzen sice ne, ale prazsky paralelni: HC Kobra Praha. Mestske casti: Vokovice, Aritma, Strešovice, Strašnice, Tesla, Vyšehrad, Motol, Hostivař, Kobylisy, Vinohrady, Podolí, Dejvice, Holešovice, Vršovice, Bohnice, Karlín, Smíchov, Žižkov, Nuseľ, Libeň, Vysočany. Stalingrad = mestska cast Prahy 7 (1949-1962, dnes Holešovice). Železničáři Praha = paralelni Lokomotiva chain. city Praha. || TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -22839,14 +23017,9 @@
           <t>L40</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>CLUB_S1993_94_0005</t>
-        </is>
-      </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Identity transition VERIFIKOVÁNA Wikipedií (D18) — genealogie: ZMP Praha → Sokol Šverma Jinonice → Spartak Motorlet Praha. Almanach 51/52 zachycuje fázi „Sokol Šverma Jinonice" s odkazem na předchůdce ZSJ ZMP Praha. (TBD odstraněn 04/2026.) || Šverma Jinonice (ZSJ ZMP Praha) 51/52 (10_liga, postup do 1.ligy). I. ČLTK Praha (Wiki D18 / D42). Genealogie: I. ČLTK Praha (1923, Český Lawn-tenisový klub) -&gt; Sokol ZMP Praha (1948) -&gt; ZSJ ZMP Praha (1949) -&gt; ZSJ Sokol Šverma Jinonice (1951) -&gt; DSO Spartak Motorlet Praha (1953) -&gt; TJ Spartak Motorlet Praha (1957) -&gt; TJ ČLTK Motorlet Praha (1969) -&gt; TJ DP I. ČLTK Praha (1970) -&gt; I. ČLTK Praha (1992). Motorlet = zavod ve čtvrti Jinonice (Praha 5). city Praha. || Praha = vsechny prazske kluby (Wiki D42 - registr ustavy 04/2026). VELKA metropole, VICE rovnocennych chains (D45 TYP 1). HLAVNI: (1) HC Sparta Praha (1903-) - dnes Tipsport ELH. (2) HC Slavia Praha (1900) - dnes 1.liga. (3) Skoda Plzen sice ne, ale prazsky paralelni: HC Kobra Praha. Mestske casti: Vokovice, Aritma, Strešovice, Strašnice, Tesla, Vyšehrad, Motol, Hostivař, Kobylisy, Vinohrady, Podolí, Dejvice, Holešovice, Vršovice, Bohnice, Karlín, Smíchov, Žižkov, Nuseľ, Libeň, Vysočany. Stalingrad = mestska cast Prahy 7 (1949-1962, dnes Holešovice). Železničáři Praha = paralelni Lokomotiva chain. city Praha.</t>
+          <t>Identity transition VERIFIKOVÁNA Wikipedií (D18) — genealogie: ZMP Praha → Sokol Šverma Jinonice → Spartak Motorlet Praha. Almanach 51/52 zachycuje fázi „Sokol Šverma Jinonice" s odkazem na předchůdce ZSJ ZMP Praha. (TBD odstraněn 04/2026.) || Šverma Jinonice (ZSJ ZMP Praha) 51/52 (10_liga, postup do 1.ligy). I. ČLTK Praha (Wiki D18 / D42). Genealogie: I. ČLTK Praha (1923, Český Lawn-tenisový klub) -&gt; Sokol ZMP Praha (1948) -&gt; ZSJ ZMP Praha (1949) -&gt; ZSJ Sokol Šverma Jinonice (1951) -&gt; DSO Spartak Motorlet Praha (1953) -&gt; TJ Spartak Motorlet Praha (1957) -&gt; TJ ČLTK Motorlet Praha (1969) -&gt; TJ DP I. ČLTK Praha (1970) -&gt; I. ČLTK Praha (1992). Motorlet = zavod ve čtvrti Jinonice (Praha 5). city Praha. || Praha = vsechny prazske kluby (Wiki D42 - registr ustavy 04/2026). VELKA metropole, VICE rovnocennych chains (D45 TYP 1). HLAVNI: (1) HC Sparta Praha (1903-) - dnes Tipsport ELH. (2) HC Slavia Praha (1900) - dnes 1.liga. (3) Skoda Plzen sice ne, ale prazsky paralelni: HC Kobra Praha. Mestske casti: Vokovice, Aritma, Strešovice, Strašnice, Tesla, Vyšehrad, Motol, Hostivař, Kobylisy, Vinohrady, Podolí, Dejvice, Holešovice, Vršovice, Bohnice, Karlín, Smíchov, Žižkov, Nuseľ, Libeň, Vysočany. Stalingrad = mestska cast Prahy 7 (1949-1962, dnes Holešovice). Železničáři Praha = paralelni Lokomotiva chain. city Praha. || TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -23007,14 +23180,9 @@
           <t>L40</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>CLUB_S1993_94_0005</t>
-        </is>
-      </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Identity transition VERIFIKOVÁNA Wikipedií (D18) — genealogie: ZMP Praha → Sokol Šverma Jinonice → Spartak Motorlet Praha. Almanach 51/52 zachycuje fázi „Sokol Šverma Jinonice" s odkazem na předchůdce ZSJ ZMP Praha. (TBD odstraněn 04/2026.) || Šverma Jinonice (ZSJ ZMP Praha) 51/52 (10_liga, postup do 1.ligy). I. ČLTK Praha (Wiki D18 / D42). Genealogie: I. ČLTK Praha (1923, Český Lawn-tenisový klub) -&gt; Sokol ZMP Praha (1948) -&gt; ZSJ ZMP Praha (1949) -&gt; ZSJ Sokol Šverma Jinonice (1951) -&gt; DSO Spartak Motorlet Praha (1953) -&gt; TJ Spartak Motorlet Praha (1957) -&gt; TJ ČLTK Motorlet Praha (1969) -&gt; TJ DP I. ČLTK Praha (1970) -&gt; I. ČLTK Praha (1992). Motorlet = zavod ve čtvrti Jinonice (Praha 5). city Praha. || Praha = vsechny prazske kluby (Wiki D42 - registr ustavy 04/2026). VELKA metropole, VICE rovnocennych chains (D45 TYP 1). HLAVNI: (1) HC Sparta Praha (1903-) - dnes Tipsport ELH. (2) HC Slavia Praha (1900) - dnes 1.liga. (3) Skoda Plzen sice ne, ale prazsky paralelni: HC Kobra Praha. Mestske casti: Vokovice, Aritma, Strešovice, Strašnice, Tesla, Vyšehrad, Motol, Hostivař, Kobylisy, Vinohrady, Podolí, Dejvice, Holešovice, Vršovice, Bohnice, Karlín, Smíchov, Žižkov, Nuseľ, Libeň, Vysočany. Stalingrad = mestska cast Prahy 7 (1949-1962, dnes Holešovice). Železničáři Praha = paralelni Lokomotiva chain. city Praha.</t>
+          <t>Identity transition VERIFIKOVÁNA Wikipedií (D18) — genealogie: ZMP Praha → Sokol Šverma Jinonice → Spartak Motorlet Praha. Almanach 51/52 zachycuje fázi „Sokol Šverma Jinonice" s odkazem na předchůdce ZSJ ZMP Praha. (TBD odstraněn 04/2026.) || Šverma Jinonice (ZSJ ZMP Praha) 51/52 (10_liga, postup do 1.ligy). I. ČLTK Praha (Wiki D18 / D42). Genealogie: I. ČLTK Praha (1923, Český Lawn-tenisový klub) -&gt; Sokol ZMP Praha (1948) -&gt; ZSJ ZMP Praha (1949) -&gt; ZSJ Sokol Šverma Jinonice (1951) -&gt; DSO Spartak Motorlet Praha (1953) -&gt; TJ Spartak Motorlet Praha (1957) -&gt; TJ ČLTK Motorlet Praha (1969) -&gt; TJ DP I. ČLTK Praha (1970) -&gt; I. ČLTK Praha (1992). Motorlet = zavod ve čtvrti Jinonice (Praha 5). city Praha. || Praha = vsechny prazske kluby (Wiki D42 - registr ustavy 04/2026). VELKA metropole, VICE rovnocennych chains (D45 TYP 1). HLAVNI: (1) HC Sparta Praha (1903-) - dnes Tipsport ELH. (2) HC Slavia Praha (1900) - dnes 1.liga. (3) Skoda Plzen sice ne, ale prazsky paralelni: HC Kobra Praha. Mestske casti: Vokovice, Aritma, Strešovice, Strašnice, Tesla, Vyšehrad, Motol, Hostivař, Kobylisy, Vinohrady, Podolí, Dejvice, Holešovice, Vršovice, Bohnice, Karlín, Smíchov, Žižkov, Nuseľ, Libeň, Vysočany. Stalingrad = mestska cast Prahy 7 (1949-1962, dnes Holešovice). Železničáři Praha = paralelni Lokomotiva chain. city Praha. || TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -23229,12 +23397,12 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov.</t>
+          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov. || TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Chomutov</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
     </row>
@@ -23313,12 +23481,12 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Chomutov = KLH VT VTJ Chomutov (Wiki D42 - registr ustavy 04/2026). Severocesky/Ustecky kraj. **KLH VT VTJ** = post-revolucni nazev (KLH = klub lední hokej, VT = vrcholový tým, VTJ = Vojenská tělovýchovná jednota). city Chomutov.</t>
+          <t>Chomutov = KLH VT VTJ Chomutov (Wiki D42 - registr ustavy 04/2026). Severocesky/Ustecky kraj. **KLH VT VTJ** = post-revolucni nazev (KLH = klub lední hokej, VT = vrcholový tým, VTJ = Vojenská tělovýchovná jednota). city Chomutov. || TBD: city 'KLH VT VTJ Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>KLH VT VTJ Chomutov</t>
+          <t>Chomutov</t>
         </is>
       </c>
     </row>
@@ -23575,12 +23743,12 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov.</t>
+          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov. || TBD: city 'Prostějov' → 'Mariánské Lázně' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Mariánské Lázně</t>
         </is>
       </c>
     </row>
@@ -24136,12 +24304,12 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Žďár nL Sázavou = TJ Žďas Žďár nL Sázavou (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihlavsky kraj. **ŽĎAS** = Žďárské strojírny a slévárny (kovaci/lisovaci stroje). 'Žďas' = lokalní pravopis. city Žďár nad Sázavou.</t>
+          <t>Žďár nL Sázavou = TJ Žďas Žďár nL Sázavou (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihlavsky kraj. **ŽĎAS** = Žďárské strojírny a slévárny (kovaci/lisovaci stroje). 'Žďas' = lokalní pravopis. city Žďár nad Sázavou. || TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>Žďas Žďár nad Sázavou</t>
+          <t>Žďár nad Sázavou</t>
         </is>
       </c>
     </row>
@@ -26292,12 +26460,12 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>Plzeň</t>
+          <t>České Budějovice</t>
         </is>
       </c>
     </row>
@@ -26334,12 +26502,12 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>Veselí nad Moravou = TJ Lokomotiva Veselí nad Moravou (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Hodonín). Železničárský klub. NE Veselí nad Lužnicí (Jihocesky). city Veselí nad Moravou.</t>
+          <t>Veselí nad Moravou = TJ Lokomotiva Veselí nad Moravou (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Hodonín). Železničárský klub. NE Veselí nad Lužnicí (Jihocesky). city Veselí nad Moravou. || TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach] || TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>Lokomotiva  Veselí nad Moravou</t>
+          <t>Veselí nad Lužnicí</t>
         </is>
       </c>
     </row>
@@ -26858,12 +27026,12 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>Plzeň</t>
+          <t>České Budějovice</t>
         </is>
       </c>
     </row>
@@ -27041,12 +27209,12 @@
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>Slovan JH = HC Vajgar/Strelci JH (Wiki D42 - registr ustavy 04/2026). Chain VBK Vajgar (1929). NE Hradec Kralove. city Jindřichův Hradec.</t>
+          <t>Slovan JH = HC Vajgar/Strelci JH (Wiki D42 - registr ustavy 04/2026). Chain VBK Vajgar (1929). NE Hradec Kralove. city Jindřichův Hradec. || TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>Vajgar Jindřichův Hradec</t>
+          <t>Jindřichův Hradec</t>
         </is>
       </c>
     </row>
@@ -27135,12 +27303,12 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>Slovan JH = HC Vajgar/Strelci JH (Wiki D42 - registr ustavy 04/2026). Chain VBK Vajgar (1929). NE Hradec Kralove. city Jindřichův Hradec.</t>
+          <t>Slovan JH = HC Vajgar/Strelci JH (Wiki D42 - registr ustavy 04/2026). Chain VBK Vajgar (1929). NE Hradec Kralove. city Jindřichův Hradec. || TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>Vajgar Jindřichův Hradec</t>
+          <t>Jindřichův Hradec</t>
         </is>
       </c>
     </row>
@@ -28606,12 +28774,12 @@
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>Klášterec nad Ohří = Sokol Klášterec (Wiki D42 - registr ustavy 04/2026). Severocesky kraj (okres Chomutov). HC Klášterec dnes mensi soutez. city Klášterec nad Ohří.</t>
+          <t>Klášterec nad Ohří = Sokol Klášterec (Wiki D42 - registr ustavy 04/2026). Severocesky kraj (okres Chomutov). HC Klášterec dnes mensi soutez. city Klášterec nad Ohří. || TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
         <is>
-          <t>Klášterec</t>
+          <t>Klášterec nad Ohří</t>
         </is>
       </c>
     </row>
@@ -28695,12 +28863,12 @@
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>Jablonec nad Nisou = TJ Bižuterie Jablonec (Wiki D42 - registr ustavy 04/2026). Severocesky/Liberecky kraj. **Bižuterie Jablonec** = sklarsky podnik (svetove znamy vyrobce bizutérie). city Jablonec nad Nisou.</t>
+          <t>Jablonec nad Nisou = TJ Bižuterie Jablonec (Wiki D42 - registr ustavy 04/2026). Severocesky/Liberecky kraj. **Bižuterie Jablonec** = sklarsky podnik (svetove znamy vyrobce bizutérie). city Jablonec nad Nisou. || TBD: city 'Bižuterie Jablonec' → 'Jablonec nad Nisou' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
         <is>
-          <t>Bižuterie Jablonec</t>
+          <t>Jablonec nad Nisou</t>
         </is>
       </c>
     </row>
@@ -29476,12 +29644,12 @@
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>Nový Bydžov = TJ Stadion Nový Bydžov (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Kralovehradecky kraj. Patterns: OSP Nový Bydžov. city Nový Bydžov.</t>
+          <t>Nový Bydžov = TJ Stadion Nový Bydžov (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Kralovehradecky kraj. Patterns: OSP Nový Bydžov. city Nový Bydžov. || TBD: city 'Stadion Nový Bydžov' → 'Nový Bydžov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J186" t="inlineStr">
         <is>
-          <t>Stadion Nový Bydžov</t>
+          <t>Nový Bydžov</t>
         </is>
       </c>
     </row>
@@ -30618,12 +30786,12 @@
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t>Uherské Hradiště = TJ Slovácká Slavia Uherské Hradiště (Wiki D42 - registr ustavy 04/2026). Zlinsky/Severomoravsky kraj. **Slovácká** = Moravske Slovacko region. city Uherské Hradiště.</t>
+          <t>Uherské Hradiště = TJ Slovácká Slavia Uherské Hradiště (Wiki D42 - registr ustavy 04/2026). Zlinsky/Severomoravsky kraj. **Slovácká** = Moravske Slovacko region. city Uherské Hradiště. || TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J212" t="inlineStr">
         <is>
-          <t>Slovácká Slavia Uherské Hradiště</t>
+          <t>Uherské Hradiště</t>
         </is>
       </c>
     </row>
@@ -34060,12 +34228,12 @@
       </c>
       <c r="I288" t="inlineStr">
         <is>
-          <t>Žďár nL Sázavou = TJ Žďas Žďár nL Sázavou (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihlavsky kraj. **ŽĎAS** = Žďárské strojírny a slévárny (kovaci/lisovaci stroje). 'Žďas' = lokalní pravopis. city Žďár nad Sázavou.</t>
+          <t>Žďár nL Sázavou = TJ Žďas Žďár nL Sázavou (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihlavsky kraj. **ŽĎAS** = Žďárské strojírny a slévárny (kovaci/lisovaci stroje). 'Žďas' = lokalní pravopis. city Žďár nad Sázavou. || TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J288" t="inlineStr">
         <is>
-          <t>Žďas Žďár nad Sázavou</t>
+          <t>Žďár nad Sázavou</t>
         </is>
       </c>
     </row>
@@ -34112,12 +34280,12 @@
       </c>
       <c r="I289" t="inlineStr">
         <is>
-          <t>Žďár nL Sázavou = TJ Žďas Žďár nL Sázavou (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihlavsky kraj. **ŽĎAS** = Žďárské strojírny a slévárny (kovaci/lisovaci stroje). 'Žďas' = lokalní pravopis. city Žďár nad Sázavou.</t>
+          <t>Žďár nL Sázavou = TJ Žďas Žďár nL Sázavou (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihlavsky kraj. **ŽĎAS** = Žďárské strojírny a slévárny (kovaci/lisovaci stroje). 'Žďas' = lokalní pravopis. city Žďár nad Sázavou. || TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J289" t="inlineStr">
         <is>
-          <t>Žďas Žďár nad Sázavou</t>
+          <t>Žďár nad Sázavou</t>
         </is>
       </c>
     </row>
@@ -35359,11 +35527,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:F36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
     <col width="26" customWidth="1" min="3" max="3"/>
     <col width="88" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
@@ -35408,21 +35576,19 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>prev_club_id</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>CLUB_S1994_95_0262</t>
+          <t>CLUB_S1994_95_0006</t>
         </is>
       </c>
       <c r="D2" s="6" t="inlineStr">
         <is>
-          <t>CLUB_S1994_95_0262 'Hrušky B' prev→CLUB_S1993_94_0340 jen dle jména (město liší) — ověřit (D24)</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
+          <t>TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -35430,21 +35596,19 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>fate</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>CLUB_S1994_95_0027</t>
+          <t>CLUB_S1994_95_0014</t>
         </is>
       </c>
       <c r="D3" s="6" t="inlineStr">
         <is>
-          <t>CLUB_S1994_95_0027 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
+          <t>TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -35452,21 +35616,19 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>fate</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>CLUB_S1994_95_0029</t>
+          <t>CLUB_S1994_95_0015</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>CLUB_S1994_95_0029 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
+          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -35474,21 +35636,19 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>fate</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>CLUB_S1994_95_0030</t>
+          <t>CLUB_S1994_95_0019</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>CLUB_S1994_95_0030 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
+          <t>TBD: city 'České Budějovice' → 'Slezan Opava' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -35496,21 +35656,19 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>fate</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>CLUB_S1994_95_0117</t>
+          <t>CLUB_S1994_95_0020</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>CLUB_S1994_95_0117 fate nekonzist. ['postup', 'reorganizace'] → 'reorganizace' (cross-ref=ano) — ověřit</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
+          <t>TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -35518,21 +35676,19 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>fate</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>CLUB_S1994_95_0118</t>
+          <t>CLUB_S1994_95_0021</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>CLUB_S1994_95_0118 fate nekonzist. ['postup', 'reorganizace'] → 'reorganizace' (cross-ref=ano) — ověřit</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
+          <t>TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -35540,21 +35696,19 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>fate</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>CLUB_S1994_95_0119</t>
+          <t>CLUB_S1994_95_0032</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>CLUB_S1994_95_0119 fate nekonzist. ['postup', 'reorganizace'] → 'reorganizace' (cross-ref=ano) — ověřit</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
+          <t>TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -35562,21 +35716,19 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>fate</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>CLUB_S1994_95_0120</t>
+          <t>CLUB_S1994_95_0035</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>CLUB_S1994_95_0120 fate nekonzist. ['postup', 'reorganizace'] → 'reorganizace' (cross-ref=ano) — ověřit</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
+          <t>TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -35584,21 +35736,19 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>fate</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>CLUB_S1994_95_0121</t>
+          <t>CLUB_S1994_95_0039</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>CLUB_S1994_95_0121 fate nekonzist. ['postup', 'reorganizace'] → 'reorganizace' (cross-ref=ano) — ověřit</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
+          <t>TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -35606,21 +35756,19 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>fate</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>CLUB_S1994_95_0159</t>
+          <t>CLUB_S1994_95_0047</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>CLUB_S1994_95_0159 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
+          <t>TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -35628,21 +35776,19 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>fate</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>CLUB_S1994_95_0162</t>
+          <t>CLUB_S1994_95_0049</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>CLUB_S1994_95_0162 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
+          <t>TBD: city 'KLH VT VTJ Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -35650,21 +35796,19 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>fate</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>CLUB_S1994_95_0186</t>
+          <t>CLUB_S1994_95_0055</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>CLUB_S1994_95_0186 fate nekonzist. ['reorganizace', 'setrval'] → 'reorganizace' (cross-ref=ano) — ověřit</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
+          <t>TBD: city 'Prostějov' → 'Mariánské Lázně' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -35672,21 +35816,19 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>fate</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>CLUB_S1994_95_0187</t>
+          <t>CLUB_S1994_95_0070</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>CLUB_S1994_95_0187 fate nekonzist. ['reorganizace', 'setrval'] → 'reorganizace' (cross-ref=ano) — ověřit</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
+          <t>TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -35694,21 +35836,19 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>fate</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>CLUB_S1994_95_0188</t>
+          <t>CLUB_S1994_95_0080</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>CLUB_S1994_95_0188 fate nekonzist. ['reorganizace', 'setrval'] → 'reorganizace' (cross-ref=ano) — ověřit</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1993_94_0096 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -35716,21 +35856,19 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>fate</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>CLUB_S1994_95_0189</t>
+          <t>CLUB_S1994_95_0107</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>CLUB_S1994_95_0189 fate nekonzist. ['reorganizace', 'setrval'] → 'reorganizace' (cross-ref=ano) — ověřit</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1993_94_0124 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -35738,21 +35876,19 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>fate</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>CLUB_S1994_95_0191</t>
+          <t>CLUB_S1994_95_0120</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>CLUB_S1994_95_0191 fate nekonzist. ['reorganizace', 'setrval'] → 'reorganizace' (cross-ref=ano) — ověřit</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
+          <t>TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -35760,21 +35896,19 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>pyramida</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>NODE_S1994_95_0020</t>
+          <t>CLUB_S1994_95_0121</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>SYSTEM NODE_S1994_95_0020 'Baráž o Extraligu' (L15, parent=NODE_S1994_95_0001) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
+          <t>TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -35782,21 +35916,19 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>pyramida</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>NODE_S1994_95_0026</t>
+          <t>CLUB_S1994_95_0121</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>SYSTEM NODE_S1994_95_0026 'Baráž o 1.ligu' (L25, parent=NODE_S1994_95_0003) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
+          <t>TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -35804,21 +35936,19 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>pyramida</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>NODE_S1994_95_0027</t>
+          <t>CLUB_S1994_95_0133</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t>SYSTEM NODE_S1994_95_0027 'Kvalifikace o 2.ligu' (L25, parent=NODE_S1994_95_0031) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
+          <t>TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -35826,24 +35956,322 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>pyramida</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>NODE_S1994_95_0035</t>
+          <t>CLUB_S1994_95_0137</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>SYSTEM NODE_S1994_95_0035 'Baráž o 1.ligu (vazba z II.ligy)' (L25, parent=NODE_S1994_95_0031) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
+          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0139</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0174</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0175</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0176</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Bižuterie Jablonec' → 'Jablonec nad Nisou' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0183</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="inlineStr">
+        <is>
+          <t>TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0184</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0195</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Stadion Nový Bydžov' → 'Nový Bydžov' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0214</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="inlineStr">
+        <is>
+          <t>TBD: K ověření, zda jde o B-tým nebo samostatný klub (Česká Třebová mohla mít dva různé kluby). Smart fix prev: 0650 (Sokol Česká Třebová = jiný klub) → 0656 (Perla II z 49/50 = B-tým Perly). Audit 04/2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0222</t>
+        </is>
+      </c>
+      <c r="D30" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0237</t>
+        </is>
+      </c>
+      <c r="D31" s="6" t="inlineStr">
+        <is>
+          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0242</t>
+        </is>
+      </c>
+      <c r="D32" s="6" t="inlineStr">
+        <is>
+          <t>TBD: clean = "(Třešť) – (Dačice)" - format meziokresni soutez nejasny. K vyjasneni Pavlem (D40). Almanach komentar ponechan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0262</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="inlineStr">
+        <is>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1993_94_0340 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0267</t>
+        </is>
+      </c>
+      <c r="D34" s="6" t="inlineStr">
+        <is>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1993_94_0358 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0299</t>
+        </is>
+      </c>
+      <c r="D35" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0300</t>
+        </is>
+      </c>
+      <c r="D36" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F21"/>
+  <autoFilter ref="A1:F36"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -41908,11 +42336,6 @@
           <t>CLUB_S1994_95_0032</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>CLUB_S1993_94_0005</t>
-        </is>
-      </c>
       <c r="U4" t="inlineStr">
         <is>
           <t>reorganizace</t>
@@ -42147,11 +42570,6 @@
           <t>CLUB_S1994_95_0035</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>CLUB_S1993_94_0005</t>
-        </is>
-      </c>
       <c r="U7" t="inlineStr">
         <is>
           <t>reorganizace</t>
@@ -42457,11 +42875,6 @@
       <c r="Q11" t="inlineStr">
         <is>
           <t>CLUB_S1994_95_0039</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>CLUB_S1993_94_0005</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">

--- a/data/S1994_95_FINAL.xlsx
+++ b/data/S1994_95_FINAL.xlsx
@@ -27,7 +27,7 @@
     <sheet name="TODO" sheetId="18" state="visible" r:id="rId18"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'TODO'!$A$1:$F$36</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'TODO'!$A$1:$F$28</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -15028,7 +15028,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D37"/>
+  <dimension ref="A1:D29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15078,7 +15078,7 @@
     <row r="3">
       <c r="C3" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -15090,7 +15090,7 @@
     <row r="4">
       <c r="C4" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -15102,7 +15102,7 @@
     <row r="5">
       <c r="C5" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -15114,7 +15114,7 @@
     <row r="6">
       <c r="C6" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'České Budějovice' → 'Slezan Opava' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -15126,7 +15126,7 @@
     <row r="7">
       <c r="C7" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -15138,7 +15138,7 @@
     <row r="8">
       <c r="C8" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -15150,7 +15150,7 @@
     <row r="9">
       <c r="C9" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'KLH VT VTJ Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -15162,7 +15162,7 @@
     <row r="10">
       <c r="C10" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -15174,7 +15174,7 @@
     <row r="11">
       <c r="C11" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1993_94_0096 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -15186,7 +15186,7 @@
     <row r="12">
       <c r="C12" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1993_94_0124 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -15198,7 +15198,7 @@
     <row r="13">
       <c r="C13" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'KLH VT VTJ Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -15210,7 +15210,7 @@
     <row r="14">
       <c r="C14" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Prostějov' → 'Mariánské Lázně' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -15222,7 +15222,7 @@
     <row r="15">
       <c r="C15" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -15234,7 +15234,7 @@
     <row r="16">
       <c r="C16" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1993_94_0096 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -15246,7 +15246,7 @@
     <row r="17">
       <c r="C17" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1993_94_0124 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>[TBD] prev_club_id / identita: TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -15258,7 +15258,7 @@
     <row r="18">
       <c r="C18" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Bižuterie Jablonec' → 'Jablonec nad Nisou' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -15270,7 +15270,7 @@
     <row r="19">
       <c r="C19" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -15282,7 +15282,7 @@
     <row r="20">
       <c r="C20" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -15294,7 +15294,7 @@
     <row r="21">
       <c r="C21" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Stadion Nový Bydžov' → 'Nový Bydžov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -15306,7 +15306,7 @@
     <row r="22">
       <c r="C22" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: K ověření, zda jde o B-tým nebo samostatný klub (Česká Třebová mohla mít dva různé kluby). Smart fix prev: 0650 (Sokol Česká Třebová = jiný klub) → 0656 (Perla II z 49/50 = B-tým Perly). Audit 04/2026.</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -15318,7 +15318,7 @@
     <row r="23">
       <c r="C23" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -15330,7 +15330,7 @@
     <row r="24">
       <c r="C24" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -15342,7 +15342,7 @@
     <row r="25">
       <c r="C25" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
+          <t>[TBD] prev_club_id / identita: TBD: clean = "(Třešť) – (Dačice)" - format meziokresni soutez nejasny. K vyjasneni Pavlem (D40). Almanach komentar ponechan.</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -15354,7 +15354,7 @@
     <row r="26">
       <c r="C26" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Bižuterie Jablonec' → 'Jablonec nad Nisou' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1993_94_0340 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -15366,7 +15366,7 @@
     <row r="27">
       <c r="C27" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1993_94_0358 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -15378,7 +15378,7 @@
     <row r="28">
       <c r="C28" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -15390,106 +15390,10 @@
     <row r="29">
       <c r="C29" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Stadion Nový Bydžov' → 'Nový Bydžov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: K ověření, zda jde o B-tým nebo samostatný klub (Česká Třebová mohla mít dva různé kluby). Smart fix prev: 0650 (Sokol Česká Třebová = jiný klub) → 0656 (Perla II z 49/50 = B-tým Perly). Audit 04/2026.</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: clean = "(Třešť) – (Dačice)" - format meziokresni soutez nejasny. K vyjasneni Pavlem (D40). Almanach komentar ponechan.</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1993_94_0340 (weak, jméno+město; verifikovat) [fix_continuity]</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1993_94_0358 (strong, jméno+město; verifikovat) [fix_continuity]</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
         <is>
           <t>TODO-auto</t>
         </is>
@@ -15506,7 +15410,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K101"/>
+  <dimension ref="A1:L101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15565,6 +15469,11 @@
           <t>note</t>
         </is>
       </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>prev_node_id</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -15607,6 +15516,11 @@
           <t>12 týmů: základ + QF/SF/finále/O3 + o udržení. Mistr: HC Dadák Vsetín.</t>
         </is>
       </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>NODE_S1993_94_0001</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -15654,6 +15568,11 @@
           <t>Vítězové 4 skupin II.ligy. Dvoukolově. Top 2 do I.ligy.</t>
         </is>
       </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>NODE_S1993_94_0002</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -15696,6 +15615,11 @@
           <t>1. liga: základní část + 1. kolo + čtvrtfinále + semifinále + O přímý sestup + Baráž o 1.ligu.</t>
         </is>
       </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>NODE_S1993_94_0003</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -15738,6 +15662,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>NODE_S1993_94_0004</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -15780,6 +15709,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>NODE_S1993_94_0005</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -15822,6 +15756,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>NODE_S1993_94_0006</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -15864,6 +15803,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>NODE_S1993_94_0007</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -15906,6 +15850,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>NODE_S1993_94_0008</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -15948,6 +15897,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>NODE_S1993_94_0009</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -15990,6 +15944,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>NODE_S1993_94_0010</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -16032,6 +15991,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>NODE_S1993_94_0011</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -16074,6 +16038,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>NODE_S1993_94_0012</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -16116,6 +16085,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>NODE_S1993_94_0013</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -16158,6 +16132,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>NODE_S1993_94_0014</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -16200,6 +16179,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>NODE_S1993_94_0015</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -16242,6 +16226,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>NODE_S1993_94_0016</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -16284,6 +16273,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>NODE_S1993_94_0017</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -16326,6 +16320,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>NODE_S1993_94_0018</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -16410,6 +16409,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>NODE_S1993_94_0020</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -16457,6 +16461,11 @@
           <t>26. kolo: Havířov - Havlíčkův Brod kontumačně 5:0 kvůli dopravní nehodě hostů.</t>
         </is>
       </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>NODE_S1993_94_0021</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -16541,6 +16550,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>NODE_S1993_94_0023</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -16588,6 +16602,11 @@
           <t>2. semifinále Brno - Havířov bylo kontumováno 5:0 po odchodu hostů z ledu.</t>
         </is>
       </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>NODE_S1993_94_0024</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -16635,6 +16654,11 @@
           <t>HC Přerov - HC Tábor 1:3. V utkáních o přímý sestup je 1., 3. a 5. utkání hráno doma.</t>
         </is>
       </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>NODE_S1993_94_0026</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -16682,6 +16706,11 @@
           <t>Šestičlenná baráž o 1. ligu. HC Slavia Becherovka Karlovy Vary a HC Přerov postupují.</t>
         </is>
       </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>NODE_S1993_94_0035</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -16729,6 +16758,11 @@
           <t>Kvalifikace o 2. ligu. V kvalifikaci je první utkání hráno doma.</t>
         </is>
       </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>NODE_S1993_94_0027</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -16771,6 +16805,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>NODE_S1993_94_0028</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -16897,6 +16936,11 @@
           <t>II.liga: 2 skupiny + finále + kvalifikace o 2.ligu. Poražený finalista Milevsko šel do baráže o 1.ligu.</t>
         </is>
       </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>NODE_S1993_94_0031</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -16944,6 +16988,11 @@
           <t>Po 17. kole převedla HC Dukla Mělník licenci do HC Stadion Litoměřice. HC Chemopetrol Litvínov B hrál domácí utkání v Teplicích.</t>
         </is>
       </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>NODE_S1993_94_0032</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -16986,6 +17035,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>NODE_S1993_94_0033</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -17033,6 +17087,11 @@
           <t>HC ZVVZ Milevsko - VTJ Jitex Písek 1:0, 2:6. Ve finále je první utkání hráno doma. Vítěz finále: VTJ Jitex Písek; poražený finalista: HC ZVVZ Milevsko.</t>
         </is>
       </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>NODE_S1993_94_0034</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -17122,6 +17181,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>NODE_S1993_94_0036</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -17164,6 +17228,11 @@
           <t>Kontejner L50</t>
         </is>
       </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>NODE_S1993_94_0037</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -17337,6 +17406,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>NODE_S1993_94_0046</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -17379,6 +17453,11 @@
           <t>Kontejner L50</t>
         </is>
       </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>NODE_S1993_94_0047</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -17421,6 +17500,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>NODE_S1993_94_0048</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -17589,6 +17673,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>NODE_S1993_94_0051</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -17631,6 +17720,11 @@
           <t>Kontejner L50</t>
         </is>
       </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>NODE_S1993_94_0052</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -17841,6 +17935,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>NODE_S1993_94_0058</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -17883,6 +17982,11 @@
           <t>Kontejner L50</t>
         </is>
       </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>NODE_S1993_94_0059</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -17925,6 +18029,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>NODE_S1993_94_0060</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -17967,6 +18076,11 @@
           <t>Kontejner L50</t>
         </is>
       </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>NODE_S1993_94_0061</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -18051,6 +18165,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>NODE_S1993_94_0062</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -18093,6 +18212,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>NODE_S1993_94_0063</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -18345,6 +18469,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>NODE_S1993_94_0068</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -18387,6 +18516,11 @@
           <t>Kontejner L50</t>
         </is>
       </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>NODE_S1993_94_0069</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -18513,6 +18647,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>NODE_S1993_94_0075</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -18555,6 +18694,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>NODE_S1993_94_0076</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -18597,6 +18741,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>NODE_S1993_94_0077</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -18639,6 +18788,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>NODE_S1993_94_0078</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -18765,6 +18919,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>NODE_S1993_94_0081</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -18807,6 +18966,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>NODE_S1993_94_0082</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -18849,6 +19013,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>NODE_S1993_94_0083</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -18891,6 +19060,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>NODE_S1993_94_0084</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -18933,6 +19107,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>NODE_S1993_94_0085</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -18975,6 +19154,11 @@
           <t>Kontejner L50</t>
         </is>
       </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>NODE_S1993_94_0086</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -19101,6 +19285,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>NODE_S1993_94_0092</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -19143,6 +19332,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>NODE_S1993_94_0093</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -19183,6 +19377,11 @@
       <c r="J86" t="inlineStr">
         <is>
           <t>complete</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>NODE_S1993_94_0094</t>
         </is>
       </c>
     </row>
@@ -19248,6 +19447,11 @@
           <t>I.liga (10 týmů, jeden stůl)</t>
         </is>
       </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>L10</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -19265,6 +19469,11 @@
           <t>NODE_S1994_95_0001</t>
         </is>
       </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>L20</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -19282,6 +19491,11 @@
           <t>NODE_S1994_95_0003</t>
         </is>
       </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>L25</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -19299,6 +19513,11 @@
           <t>NODE_S1994_95_0003</t>
         </is>
       </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>L30</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -19316,6 +19535,11 @@
           <t>NODE_S1994_95_0031</t>
         </is>
       </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -19326,6 +19550,11 @@
       <c r="B96" t="inlineStr">
         <is>
           <t>Okresní přebory (jen registr)</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>okresní</t>
         </is>
       </c>
     </row>
@@ -21786,12 +22015,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Plzeň</t>
         </is>
       </c>
     </row>
@@ -22342,12 +22571,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Slavoj České Budějovice B (Wiki D42 - registr ustavy 04/2026). B-tym hlavni Motor CB chain. city České Budějovice. || TBD: city 'České Budějovice' → 'Slezan Opava' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Slavoj České Budějovice B (Wiki D42 - registr ustavy 04/2026). B-tym hlavni Motor CB chain. city České Budějovice.</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Slezan Opava</t>
+          <t>České Budějovice</t>
         </is>
       </c>
     </row>
@@ -22389,12 +22618,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov. || TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov.</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Prostějov</t>
         </is>
       </c>
     </row>
@@ -23397,12 +23626,12 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov. || TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov.</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Chomutov</t>
         </is>
       </c>
     </row>
@@ -23743,12 +23972,12 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov. || TBD: city 'Prostějov' → 'Mariánské Lázně' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov.</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Mariánské Lázně</t>
+          <t>Prostějov</t>
         </is>
       </c>
     </row>
@@ -26460,12 +26689,12 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Plzeň</t>
         </is>
       </c>
     </row>
@@ -26502,12 +26731,12 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>Veselí nad Moravou = TJ Lokomotiva Veselí nad Moravou (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Hodonín). Železničárský klub. NE Veselí nad Lužnicí (Jihocesky). city Veselí nad Moravou. || TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach] || TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Veselí nad Moravou = TJ Lokomotiva Veselí nad Moravou (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Hodonín). Železničárský klub. NE Veselí nad Lužnicí (Jihocesky). city Veselí nad Moravou. || TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>Veselí nad Lužnicí</t>
+          <t>Veselí nad Moravou</t>
         </is>
       </c>
     </row>
@@ -27026,12 +27255,12 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Plzeň</t>
         </is>
       </c>
     </row>
@@ -35527,7 +35756,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F36"/>
+  <dimension ref="A1:F28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -35581,12 +35810,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>CLUB_S1994_95_0006</t>
+          <t>CLUB_S1994_95_0014</t>
         </is>
       </c>
       <c r="D2" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -35601,12 +35830,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>CLUB_S1994_95_0014</t>
+          <t>CLUB_S1994_95_0015</t>
         </is>
       </c>
       <c r="D3" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -35621,12 +35850,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>CLUB_S1994_95_0015</t>
+          <t>CLUB_S1994_95_0021</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -35641,12 +35870,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>CLUB_S1994_95_0019</t>
+          <t>CLUB_S1994_95_0032</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'České Budějovice' → 'Slezan Opava' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -35661,12 +35890,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>CLUB_S1994_95_0020</t>
+          <t>CLUB_S1994_95_0035</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -35681,12 +35910,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>CLUB_S1994_95_0021</t>
+          <t>CLUB_S1994_95_0039</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -35701,12 +35930,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>CLUB_S1994_95_0032</t>
+          <t>CLUB_S1994_95_0049</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
+          <t>TBD: city 'KLH VT VTJ Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -35721,12 +35950,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>CLUB_S1994_95_0035</t>
+          <t>CLUB_S1994_95_0070</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
+          <t>TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -35741,12 +35970,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>CLUB_S1994_95_0039</t>
+          <t>CLUB_S1994_95_0080</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1993_94_0096 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
     </row>
@@ -35761,12 +35990,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>CLUB_S1994_95_0047</t>
+          <t>CLUB_S1994_95_0107</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1993_94_0124 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
     </row>
@@ -35781,12 +36010,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>CLUB_S1994_95_0049</t>
+          <t>CLUB_S1994_95_0121</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'KLH VT VTJ Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -35801,12 +36030,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>CLUB_S1994_95_0055</t>
+          <t>CLUB_S1994_95_0137</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Prostějov' → 'Mariánské Lázně' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -35821,12 +36050,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>CLUB_S1994_95_0070</t>
+          <t>CLUB_S1994_95_0139</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -35841,12 +36070,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>CLUB_S1994_95_0080</t>
+          <t>CLUB_S1994_95_0174</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>TBD: auto-prev_club_id doplnění → CLUB_S1993_94_0096 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -35861,12 +36090,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>CLUB_S1994_95_0107</t>
+          <t>CLUB_S1994_95_0175</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>TBD: auto-prev_club_id doplnění → CLUB_S1993_94_0124 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
         </is>
       </c>
     </row>
@@ -35881,12 +36110,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>CLUB_S1994_95_0120</t>
+          <t>CLUB_S1994_95_0176</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Bižuterie Jablonec' → 'Jablonec nad Nisou' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -35901,12 +36130,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>CLUB_S1994_95_0121</t>
+          <t>CLUB_S1994_95_0183</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
         </is>
       </c>
     </row>
@@ -35921,12 +36150,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>CLUB_S1994_95_0121</t>
+          <t>CLUB_S1994_95_0184</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
         </is>
       </c>
     </row>
@@ -35941,12 +36170,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>CLUB_S1994_95_0133</t>
+          <t>CLUB_S1994_95_0195</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Stadion Nový Bydžov' → 'Nový Bydžov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -35961,12 +36190,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>CLUB_S1994_95_0137</t>
+          <t>CLUB_S1994_95_0214</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: K ověření, zda jde o B-tým nebo samostatný klub (Česká Třebová mohla mít dva různé kluby). Smart fix prev: 0650 (Sokol Česká Třebová = jiný klub) → 0656 (Perla II z 49/50 = B-tým Perly). Audit 04/2026.</t>
         </is>
       </c>
     </row>
@@ -35981,12 +36210,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>CLUB_S1994_95_0139</t>
+          <t>CLUB_S1994_95_0222</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -36001,12 +36230,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>CLUB_S1994_95_0174</t>
+          <t>CLUB_S1994_95_0237</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
         </is>
       </c>
     </row>
@@ -36021,12 +36250,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>CLUB_S1994_95_0175</t>
+          <t>CLUB_S1994_95_0242</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
+          <t>TBD: clean = "(Třešť) – (Dačice)" - format meziokresni soutez nejasny. K vyjasneni Pavlem (D40). Almanach komentar ponechan.</t>
         </is>
       </c>
     </row>
@@ -36041,12 +36270,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>CLUB_S1994_95_0176</t>
+          <t>CLUB_S1994_95_0262</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Bižuterie Jablonec' → 'Jablonec nad Nisou' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1993_94_0340 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
     </row>
@@ -36061,12 +36290,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>CLUB_S1994_95_0183</t>
+          <t>CLUB_S1994_95_0267</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1993_94_0358 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
     </row>
@@ -36081,12 +36310,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>CLUB_S1994_95_0184</t>
+          <t>CLUB_S1994_95_0299</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
+          <t>TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -36101,177 +36330,17 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>CLUB_S1994_95_0195</t>
+          <t>CLUB_S1994_95_0300</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Stadion Nový Bydžov' → 'Nový Bydžov' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="n">
-        <v>28</v>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>CLUB_S1994_95_0214</t>
-        </is>
-      </c>
-      <c r="D29" s="6" t="inlineStr">
-        <is>
-          <t>TBD: K ověření, zda jde o B-tým nebo samostatný klub (Česká Třebová mohla mít dva různé kluby). Smart fix prev: 0650 (Sokol Česká Třebová = jiný klub) → 0656 (Perla II z 49/50 = B-tým Perly). Audit 04/2026.</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="n">
-        <v>29</v>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>CLUB_S1994_95_0222</t>
-        </is>
-      </c>
-      <c r="D30" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="n">
-        <v>30</v>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>CLUB_S1994_95_0237</t>
-        </is>
-      </c>
-      <c r="D31" s="6" t="inlineStr">
-        <is>
-          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="n">
-        <v>31</v>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>CLUB_S1994_95_0242</t>
-        </is>
-      </c>
-      <c r="D32" s="6" t="inlineStr">
-        <is>
-          <t>TBD: clean = "(Třešť) – (Dačice)" - format meziokresni soutez nejasny. K vyjasneni Pavlem (D40). Almanach komentar ponechan.</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="n">
-        <v>32</v>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>CLUB_S1994_95_0262</t>
-        </is>
-      </c>
-      <c r="D33" s="6" t="inlineStr">
-        <is>
-          <t>TBD: auto-prev_club_id doplnění → CLUB_S1993_94_0340 (weak, jméno+město; verifikovat) [fix_continuity]</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="n">
-        <v>33</v>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>CLUB_S1994_95_0267</t>
-        </is>
-      </c>
-      <c r="D34" s="6" t="inlineStr">
-        <is>
-          <t>TBD: auto-prev_club_id doplnění → CLUB_S1993_94_0358 (strong, jméno+město; verifikovat) [fix_continuity]</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="n">
-        <v>34</v>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>CLUB_S1994_95_0299</t>
-        </is>
-      </c>
-      <c r="D35" s="6" t="inlineStr">
-        <is>
           <t>TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" t="n">
-        <v>35</v>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>CLUB_S1994_95_0300</t>
-        </is>
-      </c>
-      <c r="D36" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:F36"/>
+  <autoFilter ref="A1:F28"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/data/S1994_95_FINAL.xlsx
+++ b/data/S1994_95_FINAL.xlsx
@@ -27,7 +27,7 @@
     <sheet name="TODO" sheetId="18" state="visible" r:id="rId18"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'TODO'!$A$1:$F$28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'TODO'!$A$1:$F$32</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -15028,7 +15028,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D29"/>
+  <dimension ref="A1:D33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15394,6 +15394,54 @@
         </is>
       </c>
       <c r="D29" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>[TBD] tabulka (re-extrakce): vstřelené branky (GF) = 0/chybí — ověřit ze zdroje</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>[TBD] tabulka (re-extrakce): vstřelené branky (GF) = 0/chybí — ověřit ze zdroje</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>[TBD] tabulka (re-extrakce): vstřelené branky (GF) = 0/chybí — ověřit ze zdroje</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>[TBD] tabulka (re-extrakce): vstřelené branky (GF) = 0/chybí — ověřit ze zdroje</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
         <is>
           <t>TODO-auto</t>
         </is>
@@ -35756,7 +35804,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F28"/>
+  <dimension ref="A1:F32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -36339,8 +36387,88 @@
         </is>
       </c>
     </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>tabulka (re-extrakce)</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>HC Dadák Vsetín</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="inlineStr">
+        <is>
+          <t>vstřelené branky (GF) = 0/chybí — ověřit ze zdroje</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>tabulka (re-extrakce)</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>HC Kladno</t>
+        </is>
+      </c>
+      <c r="D30" s="6" t="inlineStr">
+        <is>
+          <t>vstřelené branky (GF) = 0/chybí — ověřit ze zdroje</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>tabulka (re-extrakce)</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>HC České Budějovice</t>
+        </is>
+      </c>
+      <c r="D31" s="6" t="inlineStr">
+        <is>
+          <t>vstřelené branky (GF) = 0/chybí — ověřit ze zdroje</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>tabulka (re-extrakce)</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>HC Slavia Praha</t>
+        </is>
+      </c>
+      <c r="D32" s="6" t="inlineStr">
+        <is>
+          <t>vstřelené branky (GF) = 0/chybí — ověřit ze zdroje</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F28"/>
+  <autoFilter ref="A1:F32"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/data/S1994_95_FINAL.xlsx
+++ b/data/S1994_95_FINAL.xlsx
@@ -27,7 +27,7 @@
     <sheet name="TODO" sheetId="18" state="visible" r:id="rId18"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'TODO'!$A$1:$F$32</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'TODO'!$A$1:$F$28</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -762,16 +762,16 @@
         <v>44</v>
       </c>
       <c r="G5" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="H5" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="I5" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>141</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -779,7 +779,10 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>141</v>
+        <v>107</v>
+      </c>
+      <c r="M5" t="n">
+        <v>54</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -837,16 +840,16 @@
         <v>44</v>
       </c>
       <c r="G6" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H6" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I6" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>178</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -854,7 +857,10 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>178</v>
+        <v>142</v>
+      </c>
+      <c r="M6" t="n">
+        <v>54</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -912,16 +918,16 @@
         <v>44</v>
       </c>
       <c r="G7" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H7" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="I7" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="J7" t="n">
-        <v>1</v>
+        <v>130</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -929,7 +935,10 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>130</v>
+        <v>124</v>
+      </c>
+      <c r="M7" t="n">
+        <v>48</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -987,16 +996,16 @@
         <v>44</v>
       </c>
       <c r="G8" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H8" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="I8" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="J8" t="n">
-        <v>3</v>
+        <v>158</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1004,7 +1013,10 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>158</v>
+        <v>149</v>
+      </c>
+      <c r="M8" t="n">
+        <v>48</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
@@ -1065,13 +1077,13 @@
         <v>16</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="I9" t="n">
         <v>14</v>
       </c>
       <c r="J9" t="n">
-        <v>2</v>
+        <v>118</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1079,7 +1091,10 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>118</v>
+        <v>112</v>
+      </c>
+      <c r="M9" t="n">
+        <v>46</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
@@ -1140,13 +1155,13 @@
         <v>20</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I10" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>142</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1154,7 +1169,10 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>142</v>
+        <v>124</v>
+      </c>
+      <c r="M10" t="n">
+        <v>46</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -1217,16 +1235,16 @@
         <v>44</v>
       </c>
       <c r="G11" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H11" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="I11" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>133</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1234,7 +1252,10 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>133</v>
+        <v>164</v>
+      </c>
+      <c r="M11" t="n">
+        <v>43</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -1295,13 +1316,13 @@
         <v>18</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I12" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="J12" t="n">
-        <v>1</v>
+        <v>149</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1309,7 +1330,10 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>149</v>
+        <v>143</v>
+      </c>
+      <c r="M12" t="n">
+        <v>42</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
@@ -1367,16 +1391,16 @@
         <v>44</v>
       </c>
       <c r="G13" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H13" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="I13" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="J13" t="n">
-        <v>1</v>
+        <v>123</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1384,7 +1408,10 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>123</v>
+        <v>129</v>
+      </c>
+      <c r="M13" t="n">
+        <v>41</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
@@ -1442,16 +1469,16 @@
         <v>44</v>
       </c>
       <c r="G14" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H14" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I14" t="n">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="J14" t="n">
-        <v>3</v>
+        <v>144</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -1459,7 +1486,10 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>144</v>
+        <v>156</v>
+      </c>
+      <c r="M14" t="n">
+        <v>41</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
@@ -1517,16 +1547,16 @@
         <v>44</v>
       </c>
       <c r="G15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H15" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="I15" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="J15" t="n">
-        <v>1</v>
+        <v>134</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -1534,7 +1564,10 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>134</v>
+        <v>151</v>
+      </c>
+      <c r="M15" t="n">
+        <v>37</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
@@ -1592,16 +1625,16 @@
         <v>44</v>
       </c>
       <c r="G16" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H16" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I16" t="n">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="J16" t="n">
-        <v>2</v>
+        <v>117</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -1609,7 +1642,10 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>117</v>
+        <v>166</v>
+      </c>
+      <c r="M16" t="n">
+        <v>28</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
@@ -2108,16 +2144,16 @@
         <v>50</v>
       </c>
       <c r="G30" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H30" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="I30" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="J30" t="n">
-        <v>1</v>
+        <v>145</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
@@ -2125,7 +2161,10 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>145</v>
+        <v>146</v>
+      </c>
+      <c r="M30" t="n">
+        <v>48</v>
       </c>
       <c r="N30" t="inlineStr">
         <is>
@@ -2183,16 +2222,16 @@
         <v>50</v>
       </c>
       <c r="G31" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H31" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="I31" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="J31" t="n">
-        <v>1</v>
+        <v>158</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
@@ -2200,7 +2239,10 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>158</v>
+        <v>169</v>
+      </c>
+      <c r="M31" t="n">
+        <v>46</v>
       </c>
       <c r="N31" t="inlineStr">
         <is>
@@ -2258,16 +2300,16 @@
         <v>50</v>
       </c>
       <c r="G32" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H32" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I32" t="n">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="J32" t="n">
-        <v>3</v>
+        <v>163</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
@@ -2275,7 +2317,10 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>163</v>
+        <v>184</v>
+      </c>
+      <c r="M32" t="n">
+        <v>44</v>
       </c>
       <c r="N32" t="inlineStr">
         <is>
@@ -2333,16 +2378,16 @@
         <v>50</v>
       </c>
       <c r="G33" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H33" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I33" t="n">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="J33" t="n">
-        <v>2</v>
+        <v>141</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
@@ -2350,7 +2395,10 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>141</v>
+        <v>192</v>
+      </c>
+      <c r="M33" t="n">
+        <v>33</v>
       </c>
       <c r="N33" t="inlineStr">
         <is>
@@ -15028,7 +15076,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D33"/>
+  <dimension ref="A1:D29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15394,54 +15442,6 @@
         </is>
       </c>
       <c r="D29" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>[TBD] tabulka (re-extrakce): vstřelené branky (GF) = 0/chybí — ověřit ze zdroje</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>[TBD] tabulka (re-extrakce): vstřelené branky (GF) = 0/chybí — ověřit ze zdroje</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>[TBD] tabulka (re-extrakce): vstřelené branky (GF) = 0/chybí — ověřit ze zdroje</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>[TBD] tabulka (re-extrakce): vstřelené branky (GF) = 0/chybí — ověřit ze zdroje</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
         <is>
           <t>TODO-auto</t>
         </is>
@@ -35804,7 +35804,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F32"/>
+  <dimension ref="A1:F28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -36387,88 +36387,8 @@
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" t="n">
-        <v>28</v>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>tabulka (re-extrakce)</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>HC Dadák Vsetín</t>
-        </is>
-      </c>
-      <c r="D29" s="6" t="inlineStr">
-        <is>
-          <t>vstřelené branky (GF) = 0/chybí — ověřit ze zdroje</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="n">
-        <v>29</v>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>tabulka (re-extrakce)</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>HC Kladno</t>
-        </is>
-      </c>
-      <c r="D30" s="6" t="inlineStr">
-        <is>
-          <t>vstřelené branky (GF) = 0/chybí — ověřit ze zdroje</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="n">
-        <v>30</v>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>tabulka (re-extrakce)</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>HC České Budějovice</t>
-        </is>
-      </c>
-      <c r="D31" s="6" t="inlineStr">
-        <is>
-          <t>vstřelené branky (GF) = 0/chybí — ověřit ze zdroje</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="n">
-        <v>31</v>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>tabulka (re-extrakce)</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>HC Slavia Praha</t>
-        </is>
-      </c>
-      <c r="D32" s="6" t="inlineStr">
-        <is>
-          <t>vstřelené branky (GF) = 0/chybí — ověřit ze zdroje</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:F32"/>
+  <autoFilter ref="A1:F28"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/data/S1994_95_FINAL.xlsx
+++ b/data/S1994_95_FINAL.xlsx
@@ -39083,7 +39083,7 @@
         <v>5</v>
       </c>
       <c r="J5" t="n">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -39567,7 +39567,7 @@
         <v>92</v>
       </c>
       <c r="M11" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -40042,7 +40042,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="M17" t="n">
         <v>18</v>
@@ -40479,7 +40479,7 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="M23" t="n">
         <v>44</v>
@@ -41100,7 +41100,7 @@
         <v>14</v>
       </c>
       <c r="J31" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>

--- a/data/S1994_95_FINAL.xlsx
+++ b/data/S1994_95_FINAL.xlsx
@@ -15458,7 +15458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L101"/>
+  <dimension ref="A1:N101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15522,6 +15522,16 @@
           <t>prev_node_id</t>
         </is>
       </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>entry</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>phase_order</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -19475,8 +19485,6 @@
         </is>
       </c>
     </row>
-    <row r="88"/>
-    <row r="89"/>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
@@ -19606,7 +19614,6 @@
         </is>
       </c>
     </row>
-    <row r="97"/>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>

--- a/data/S1994_95_FINAL.xlsx
+++ b/data/S1994_95_FINAL.xlsx
@@ -15710,6 +15710,16 @@
           <t>NODE_S1994_95_0001</t>
         </is>
       </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>NODE_S1994_95_0009</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>NODE_S1994_95_0015</t>
+        </is>
+      </c>
       <c r="I5" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -15724,6 +15734,14 @@
         <is>
           <t>NODE_S1993_94_0004</t>
         </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>12 týmů</t>
+        </is>
+      </c>
+      <c r="N5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -15898,6 +15916,16 @@
           <t>NODE_S1994_95_0007</t>
         </is>
       </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>NODE_S1994_95_0009</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>NODE_S1994_95_0018</t>
+        </is>
+      </c>
       <c r="I9" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -15912,6 +15940,14 @@
         <is>
           <t>NODE_S1993_94_0008</t>
         </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>horní část ZČ</t>
+        </is>
+      </c>
+      <c r="N9" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -15945,6 +15981,16 @@
           <t>NODE_S1994_95_0007</t>
         </is>
       </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>NODE_S1994_95_0010</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>NODE_S1994_95_0018</t>
+        </is>
+      </c>
       <c r="I10" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -15959,6 +16005,14 @@
         <is>
           <t>NODE_S1993_94_0009</t>
         </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>1.–8. ZČ</t>
+        </is>
+      </c>
+      <c r="N10" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -15992,6 +16046,16 @@
           <t>NODE_S1994_95_0007</t>
         </is>
       </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>NODE_S1994_95_0014</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>NODE_S1994_95_0013</t>
+        </is>
+      </c>
       <c r="I11" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -16006,6 +16070,14 @@
         <is>
           <t>NODE_S1993_94_0010</t>
         </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>vítězové ČF</t>
+        </is>
+      </c>
+      <c r="N11" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="12">
@@ -16039,6 +16111,8 @@
           <t>NODE_S1994_95_0007</t>
         </is>
       </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -16053,6 +16127,14 @@
         <is>
           <t>NODE_S1993_94_0011</t>
         </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>sk. o 5.–8. (dolní)</t>
+        </is>
+      </c>
+      <c r="N12" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="13">
@@ -16086,6 +16168,8 @@
           <t>NODE_S1994_95_0007</t>
         </is>
       </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -16100,6 +16184,14 @@
         <is>
           <t>NODE_S1993_94_0012</t>
         </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>sk. o 5.–8. (horní)</t>
+        </is>
+      </c>
+      <c r="N13" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="14">
@@ -16133,6 +16225,8 @@
           <t>NODE_S1994_95_0007</t>
         </is>
       </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -16147,6 +16241,14 @@
         <is>
           <t>NODE_S1993_94_0013</t>
         </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>poražení SF</t>
+        </is>
+      </c>
+      <c r="N14" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="15">
@@ -16180,6 +16282,8 @@
           <t>NODE_S1994_95_0007</t>
         </is>
       </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -16194,6 +16298,14 @@
         <is>
           <t>NODE_S1993_94_0014</t>
         </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N15" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="16">
@@ -16227,6 +16339,8 @@
           <t>NODE_S1994_95_0001</t>
         </is>
       </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -16241,6 +16355,14 @@
         <is>
           <t>NODE_S1993_94_0015</t>
         </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>9.–12. ZČ</t>
+        </is>
+      </c>
+      <c r="N16" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="17">
@@ -16274,6 +16396,8 @@
           <t>NODE_S1994_95_0007</t>
         </is>
       </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -16288,6 +16412,14 @@
         <is>
           <t>NODE_S1993_94_0016</t>
         </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>poražení play-off</t>
+        </is>
+      </c>
+      <c r="N17" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="18">
@@ -16321,6 +16453,8 @@
           <t>NODE_S1994_95_0007</t>
         </is>
       </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -16335,6 +16469,14 @@
         <is>
           <t>NODE_S1993_94_0017</t>
         </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>o 9. místo</t>
+        </is>
+      </c>
+      <c r="N18" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="19">
@@ -16368,6 +16510,16 @@
           <t>NODE_S1994_95_0007</t>
         </is>
       </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>NODE_S1994_95_0012</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>NODE_S1994_95_0011</t>
+        </is>
+      </c>
       <c r="I19" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -16382,6 +16534,14 @@
         <is>
           <t>NODE_S1993_94_0018</t>
         </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>poražení ČF</t>
+        </is>
+      </c>
+      <c r="N19" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="20">
@@ -16504,6 +16664,12 @@
           <t>NODE_S1994_95_0003</t>
         </is>
       </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>NODE_S1994_95_0023</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -16523,6 +16689,14 @@
         <is>
           <t>NODE_S1993_94_0021</t>
         </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>14 týmů</t>
+        </is>
+      </c>
+      <c r="N22" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -16598,6 +16772,12 @@
           <t>NODE_S1994_95_0003</t>
         </is>
       </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>NODE_S1994_95_0024</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -16612,6 +16792,14 @@
         <is>
           <t>NODE_S1993_94_0023</t>
         </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>horní polovina ZČ</t>
+        </is>
+      </c>
+      <c r="N24" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="25">
@@ -16645,6 +16833,8 @@
           <t>NODE_S1994_95_0003</t>
         </is>
       </c>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -16664,6 +16854,14 @@
         <is>
           <t>NODE_S1993_94_0024</t>
         </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>vítězové ČF</t>
+        </is>
+      </c>
+      <c r="N25" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="26">
@@ -17130,6 +17328,8 @@
           <t>NODE_S1994_95_0031</t>
         </is>
       </c>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -17149,6 +17349,14 @@
         <is>
           <t>NODE_S1993_94_0034</t>
         </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N35" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="36">
@@ -17548,6 +17756,8 @@
           <t>NODE_S1994_95_0041</t>
         </is>
       </c>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -17562,6 +17772,14 @@
         <is>
           <t>NODE_S1993_94_0048</t>
         </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>11 týmů</t>
+        </is>
+      </c>
+      <c r="N44" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -17637,6 +17855,8 @@
           <t>NODE_S1994_95_0041</t>
         </is>
       </c>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -17646,6 +17866,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>sk. o 5.–8. (horní)</t>
+        </is>
+      </c>
+      <c r="N46" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="47">
@@ -18213,6 +18441,12 @@
           <t>NODE_S1994_95_0056</t>
         </is>
       </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>NODE_S1994_95_0064</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -18227,6 +18461,14 @@
         <is>
           <t>NODE_S1993_94_0062</t>
         </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>10 týmů</t>
+        </is>
+      </c>
+      <c r="N59" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -18307,6 +18549,8 @@
           <t>NODE_S1994_95_0056</t>
         </is>
       </c>
+      <c r="G61" t="inlineStr"/>
+      <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -18316,6 +18560,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>sk. o 5.–8. (horní)</t>
+        </is>
+      </c>
+      <c r="N61" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="62">
@@ -18475,6 +18727,8 @@
           <t>NODE_S1994_95_0056</t>
         </is>
       </c>
+      <c r="G65" t="inlineStr"/>
+      <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -18484,6 +18738,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N65" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="66">
@@ -18967,6 +19229,8 @@
           <t>NODE_S1994_95_0066</t>
         </is>
       </c>
+      <c r="G76" t="inlineStr"/>
+      <c r="H76" t="inlineStr"/>
       <c r="I76" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -18981,6 +19245,14 @@
         <is>
           <t>NODE_S1993_94_0081</t>
         </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>dolní část ZČ</t>
+        </is>
+      </c>
+      <c r="N76" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="77">
@@ -19014,6 +19286,8 @@
           <t>NODE_S1994_95_0066</t>
         </is>
       </c>
+      <c r="G77" t="inlineStr"/>
+      <c r="H77" t="inlineStr"/>
       <c r="I77" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -19028,6 +19302,14 @@
         <is>
           <t>NODE_S1993_94_0082</t>
         </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>dolní část ZČ</t>
+        </is>
+      </c>
+      <c r="N77" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="78">
@@ -19061,6 +19343,8 @@
           <t>NODE_S1994_95_0066</t>
         </is>
       </c>
+      <c r="G78" t="inlineStr"/>
+      <c r="H78" t="inlineStr"/>
       <c r="I78" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -19075,6 +19359,14 @@
         <is>
           <t>NODE_S1993_94_0083</t>
         </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>dolní část ZČ</t>
+        </is>
+      </c>
+      <c r="N78" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="79">
@@ -19108,6 +19400,8 @@
           <t>NODE_S1994_95_0066</t>
         </is>
       </c>
+      <c r="G79" t="inlineStr"/>
+      <c r="H79" t="inlineStr"/>
       <c r="I79" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -19122,6 +19416,14 @@
         <is>
           <t>NODE_S1993_94_0084</t>
         </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>dolní část ZČ</t>
+        </is>
+      </c>
+      <c r="N79" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="80">
@@ -19474,6 +19776,8 @@
           <t>NODE_S1994_95_0080</t>
         </is>
       </c>
+      <c r="G87" t="inlineStr"/>
+      <c r="H87" t="inlineStr"/>
       <c r="I87" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -19484,7 +19788,17 @@
           <t>complete</t>
         </is>
       </c>
-    </row>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>sk. o 5.–8. (dolní)</t>
+        </is>
+      </c>
+      <c r="N87" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="88"/>
+    <row r="89"/>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
@@ -19614,6 +19928,7 @@
         </is>
       </c>
     </row>
+    <row r="97"/>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>

--- a/data/S1994_95_FINAL.xlsx
+++ b/data/S1994_95_FINAL.xlsx
@@ -755,7 +755,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>M</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -16111,8 +16111,6 @@
           <t>NODE_S1994_95_0007</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -16168,8 +16166,6 @@
           <t>NODE_S1994_95_0007</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -16225,8 +16221,6 @@
           <t>NODE_S1994_95_0007</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -16282,8 +16276,6 @@
           <t>NODE_S1994_95_0007</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -16339,8 +16331,6 @@
           <t>NODE_S1994_95_0001</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -16396,8 +16386,6 @@
           <t>NODE_S1994_95_0007</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -16453,8 +16441,6 @@
           <t>NODE_S1994_95_0007</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -16669,7 +16655,6 @@
           <t>NODE_S1994_95_0023</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -16777,7 +16762,6 @@
           <t>NODE_S1994_95_0024</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -16833,8 +16817,6 @@
           <t>NODE_S1994_95_0003</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -17328,8 +17310,6 @@
           <t>NODE_S1994_95_0031</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -17756,8 +17736,6 @@
           <t>NODE_S1994_95_0041</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr"/>
-      <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -17855,8 +17833,6 @@
           <t>NODE_S1994_95_0041</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -18446,7 +18422,6 @@
           <t>NODE_S1994_95_0064</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -18549,8 +18524,6 @@
           <t>NODE_S1994_95_0056</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr"/>
-      <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -18727,8 +18700,6 @@
           <t>NODE_S1994_95_0056</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr"/>
-      <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -19229,8 +19200,6 @@
           <t>NODE_S1994_95_0066</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr"/>
-      <c r="H76" t="inlineStr"/>
       <c r="I76" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -19286,8 +19255,6 @@
           <t>NODE_S1994_95_0066</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr"/>
-      <c r="H77" t="inlineStr"/>
       <c r="I77" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -19343,8 +19310,6 @@
           <t>NODE_S1994_95_0066</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr"/>
-      <c r="H78" t="inlineStr"/>
       <c r="I78" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -19400,8 +19365,6 @@
           <t>NODE_S1994_95_0066</t>
         </is>
       </c>
-      <c r="G79" t="inlineStr"/>
-      <c r="H79" t="inlineStr"/>
       <c r="I79" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -19776,8 +19739,6 @@
           <t>NODE_S1994_95_0080</t>
         </is>
       </c>
-      <c r="G87" t="inlineStr"/>
-      <c r="H87" t="inlineStr"/>
       <c r="I87" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -19797,8 +19758,6 @@
         <v>5</v>
       </c>
     </row>
-    <row r="88"/>
-    <row r="89"/>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
@@ -19928,7 +19887,6 @@
         </is>
       </c>
     </row>
-    <row r="97"/>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
@@ -35848,7 +35806,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B22"/>
+  <dimension ref="A1:B23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36112,6 +36070,18 @@
       <c r="B22" t="inlineStr">
         <is>
           <t>V kvalifikaci o 2. ligu je první utkání hráno doma.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>mistr</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>HC Dadák Vsetín</t>
         </is>
       </c>
     </row>

--- a/data/S1994_95_FINAL.xlsx
+++ b/data/S1994_95_FINAL.xlsx
@@ -19758,6 +19758,8 @@
         <v>5</v>
       </c>
     </row>
+    <row r="88"/>
+    <row r="89"/>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
@@ -19887,6 +19889,7 @@
         </is>
       </c>
     </row>
+    <row r="97"/>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>

--- a/data/S1994_95_FINAL.xlsx
+++ b/data/S1994_95_FINAL.xlsx
@@ -2447,7 +2447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W59"/>
+  <dimension ref="A1:W68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -6541,6 +6541,388 @@
         </is>
       </c>
     </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Havlíčkův Brod</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>NODE_S1994_95_0089</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>1</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Nekoř</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>Havlíčkův Brod</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>NODE_S1994_95_0089</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0377</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>TR_S1994_95_00297</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>2</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Třebovice</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>Havlíčkův Brod</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>NODE_S1994_95_0089</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0378</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>TR_S1994_95_00298</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>3</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Česká Třebová</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>Havlíčkův Brod</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>NODE_S1994_95_0089</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0379</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>TR_S1994_95_00299</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>4</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Dlouhoňovice</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>Havlíčkův Brod</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>NODE_S1994_95_0089</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0380</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>TR_S1994_95_00300</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>5</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Králíky</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>Havlíčkův Brod</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>NODE_S1994_95_0089</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0381</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>TR_S1994_95_00301</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>6</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Lanškroun</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>Havlíčkův Brod</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>NODE_S1994_95_0089</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0382</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>TR_S1994_95_00302</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>7</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Voděrady</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>Havlíčkův Brod</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>NODE_S1994_95_0089</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0383</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>TR_S1994_95_00303</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>8</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Řetová</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>Havlíčkův Brod</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>NODE_S1994_95_0089</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q68" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0384</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>TR_S1994_95_00304</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6552,7 +6934,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W102"/>
+  <dimension ref="A1:W154"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -12516,6 +12898,2360 @@
         </is>
       </c>
     </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>KP I.třídy</t>
+        </is>
+      </c>
+      <c r="O103" t="inlineStr">
+        <is>
+          <t>NODE_S1994_95_0090</t>
+        </is>
+      </c>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C104" t="n">
+        <v>6</v>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Malhostovice</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N104" t="inlineStr">
+        <is>
+          <t>KP I.třídy</t>
+        </is>
+      </c>
+      <c r="O104" t="inlineStr">
+        <is>
+          <t>NODE_S1994_95_0090</t>
+        </is>
+      </c>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q104" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0385</t>
+        </is>
+      </c>
+      <c r="V104" t="inlineStr">
+        <is>
+          <t>TR_S1994_95_00305</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Blansko</t>
+        </is>
+      </c>
+      <c r="O105" t="inlineStr">
+        <is>
+          <t>NODE_S1994_95_0091</t>
+        </is>
+      </c>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C106" t="n">
+        <v>1</v>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Sloup</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N106" t="inlineStr">
+        <is>
+          <t>Blansko</t>
+        </is>
+      </c>
+      <c r="O106" t="inlineStr">
+        <is>
+          <t>NODE_S1994_95_0091</t>
+        </is>
+      </c>
+      <c r="P106" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q106" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0386</t>
+        </is>
+      </c>
+      <c r="V106" t="inlineStr">
+        <is>
+          <t>TR_S1994_95_00306</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C107" t="n">
+        <v>2</v>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Bořitov</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N107" t="inlineStr">
+        <is>
+          <t>Blansko</t>
+        </is>
+      </c>
+      <c r="O107" t="inlineStr">
+        <is>
+          <t>NODE_S1994_95_0091</t>
+        </is>
+      </c>
+      <c r="P107" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q107" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0387</t>
+        </is>
+      </c>
+      <c r="V107" t="inlineStr">
+        <is>
+          <t>TR_S1994_95_00307</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C108" t="n">
+        <v>3</v>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Vilémovice</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N108" t="inlineStr">
+        <is>
+          <t>Blansko</t>
+        </is>
+      </c>
+      <c r="O108" t="inlineStr">
+        <is>
+          <t>NODE_S1994_95_0091</t>
+        </is>
+      </c>
+      <c r="P108" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q108" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0388</t>
+        </is>
+      </c>
+      <c r="V108" t="inlineStr">
+        <is>
+          <t>TR_S1994_95_00308</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C109" t="n">
+        <v>4</v>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Kunštát</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N109" t="inlineStr">
+        <is>
+          <t>Blansko</t>
+        </is>
+      </c>
+      <c r="O109" t="inlineStr">
+        <is>
+          <t>NODE_S1994_95_0091</t>
+        </is>
+      </c>
+      <c r="P109" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q109" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0389</t>
+        </is>
+      </c>
+      <c r="V109" t="inlineStr">
+        <is>
+          <t>TR_S1994_95_00309</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C110" t="n">
+        <v>1</v>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Technika Brno</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N110" t="inlineStr">
+        <is>
+          <t>Blansko</t>
+        </is>
+      </c>
+      <c r="O110" t="inlineStr">
+        <is>
+          <t>NODE_S1994_95_0091</t>
+        </is>
+      </c>
+      <c r="P110" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q110" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0390</t>
+        </is>
+      </c>
+      <c r="V110" t="inlineStr">
+        <is>
+          <t>TR_S1994_95_00310</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C111" t="n">
+        <v>2</v>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Hrušky B</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N111" t="inlineStr">
+        <is>
+          <t>Blansko</t>
+        </is>
+      </c>
+      <c r="O111" t="inlineStr">
+        <is>
+          <t>NODE_S1994_95_0091</t>
+        </is>
+      </c>
+      <c r="P111" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q111" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0391</t>
+        </is>
+      </c>
+      <c r="V111" t="inlineStr">
+        <is>
+          <t>TR_S1994_95_00311</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C112" t="n">
+        <v>3</v>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Šerkovice</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N112" t="inlineStr">
+        <is>
+          <t>Blansko</t>
+        </is>
+      </c>
+      <c r="O112" t="inlineStr">
+        <is>
+          <t>NODE_S1994_95_0091</t>
+        </is>
+      </c>
+      <c r="P112" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q112" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0392</t>
+        </is>
+      </c>
+      <c r="V112" t="inlineStr">
+        <is>
+          <t>TR_S1994_95_00312</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C113" t="n">
+        <v>4</v>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Lelekovice</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N113" t="inlineStr">
+        <is>
+          <t>Blansko</t>
+        </is>
+      </c>
+      <c r="O113" t="inlineStr">
+        <is>
+          <t>NODE_S1994_95_0091</t>
+        </is>
+      </c>
+      <c r="P113" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q113" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0393</t>
+        </is>
+      </c>
+      <c r="V113" t="inlineStr">
+        <is>
+          <t>TR_S1994_95_00313</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C114" t="n">
+        <v>5</v>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Oslavany</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N114" t="inlineStr">
+        <is>
+          <t>Blansko</t>
+        </is>
+      </c>
+      <c r="O114" t="inlineStr">
+        <is>
+          <t>NODE_S1994_95_0091</t>
+        </is>
+      </c>
+      <c r="P114" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q114" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0394</t>
+        </is>
+      </c>
+      <c r="V114" t="inlineStr">
+        <is>
+          <t>TR_S1994_95_00314</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C115" t="n">
+        <v>6</v>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Starý Lískovec</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N115" t="inlineStr">
+        <is>
+          <t>Blansko</t>
+        </is>
+      </c>
+      <c r="O115" t="inlineStr">
+        <is>
+          <t>NODE_S1994_95_0091</t>
+        </is>
+      </c>
+      <c r="P115" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q115" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0395</t>
+        </is>
+      </c>
+      <c r="V115" t="inlineStr">
+        <is>
+          <t>TR_S1994_95_00315</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C116" t="n">
+        <v>1</v>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Dačice</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N116" t="inlineStr">
+        <is>
+          <t>Blansko</t>
+        </is>
+      </c>
+      <c r="O116" t="inlineStr">
+        <is>
+          <t>NODE_S1994_95_0091</t>
+        </is>
+      </c>
+      <c r="P116" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q116" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0396</t>
+        </is>
+      </c>
+      <c r="V116" t="inlineStr">
+        <is>
+          <t>TR_S1994_95_00316</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C117" t="n">
+        <v>2</v>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Polná</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N117" t="inlineStr">
+        <is>
+          <t>Blansko</t>
+        </is>
+      </c>
+      <c r="O117" t="inlineStr">
+        <is>
+          <t>NODE_S1994_95_0091</t>
+        </is>
+      </c>
+      <c r="P117" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q117" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0397</t>
+        </is>
+      </c>
+      <c r="V117" t="inlineStr">
+        <is>
+          <t>TR_S1994_95_00317</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C118" t="n">
+        <v>3</v>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Růžená</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N118" t="inlineStr">
+        <is>
+          <t>Blansko</t>
+        </is>
+      </c>
+      <c r="O118" t="inlineStr">
+        <is>
+          <t>NODE_S1994_95_0091</t>
+        </is>
+      </c>
+      <c r="P118" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q118" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0398</t>
+        </is>
+      </c>
+      <c r="V118" t="inlineStr">
+        <is>
+          <t>TR_S1994_95_00318</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C119" t="n">
+        <v>4</v>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Puklice</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N119" t="inlineStr">
+        <is>
+          <t>Blansko</t>
+        </is>
+      </c>
+      <c r="O119" t="inlineStr">
+        <is>
+          <t>NODE_S1994_95_0091</t>
+        </is>
+      </c>
+      <c r="P119" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q119" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0399</t>
+        </is>
+      </c>
+      <c r="V119" t="inlineStr">
+        <is>
+          <t>TR_S1994_95_00319</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C120" t="n">
+        <v>5</v>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Brtnice</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N120" t="inlineStr">
+        <is>
+          <t>Blansko</t>
+        </is>
+      </c>
+      <c r="O120" t="inlineStr">
+        <is>
+          <t>NODE_S1994_95_0091</t>
+        </is>
+      </c>
+      <c r="P120" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q120" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0400</t>
+        </is>
+      </c>
+      <c r="V120" t="inlineStr">
+        <is>
+          <t>TR_S1994_95_00320</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C121" t="n">
+        <v>1</v>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>SKP Kroměříž</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N121" t="inlineStr">
+        <is>
+          <t>Blansko</t>
+        </is>
+      </c>
+      <c r="O121" t="inlineStr">
+        <is>
+          <t>NODE_S1994_95_0091</t>
+        </is>
+      </c>
+      <c r="P121" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q121" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0401</t>
+        </is>
+      </c>
+      <c r="V121" t="inlineStr">
+        <is>
+          <t>TR_S1994_95_00321</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C122" t="n">
+        <v>2</v>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Milenov</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N122" t="inlineStr">
+        <is>
+          <t>Blansko</t>
+        </is>
+      </c>
+      <c r="O122" t="inlineStr">
+        <is>
+          <t>NODE_S1994_95_0091</t>
+        </is>
+      </c>
+      <c r="P122" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q122" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0402</t>
+        </is>
+      </c>
+      <c r="V122" t="inlineStr">
+        <is>
+          <t>TR_S1994_95_00322</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C123" t="n">
+        <v>3</v>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Zborovice</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N123" t="inlineStr">
+        <is>
+          <t>Blansko</t>
+        </is>
+      </c>
+      <c r="O123" t="inlineStr">
+        <is>
+          <t>NODE_S1994_95_0091</t>
+        </is>
+      </c>
+      <c r="P123" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q123" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0403</t>
+        </is>
+      </c>
+      <c r="V123" t="inlineStr">
+        <is>
+          <t>TR_S1994_95_00323</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C124" t="n">
+        <v>4</v>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Troubky</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N124" t="inlineStr">
+        <is>
+          <t>Blansko</t>
+        </is>
+      </c>
+      <c r="O124" t="inlineStr">
+        <is>
+          <t>NODE_S1994_95_0091</t>
+        </is>
+      </c>
+      <c r="P124" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q124" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0404</t>
+        </is>
+      </c>
+      <c r="V124" t="inlineStr">
+        <is>
+          <t>TR_S1994_95_00324</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C125" t="n">
+        <v>5</v>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Citov</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N125" t="inlineStr">
+        <is>
+          <t>Blansko</t>
+        </is>
+      </c>
+      <c r="O125" t="inlineStr">
+        <is>
+          <t>NODE_S1994_95_0091</t>
+        </is>
+      </c>
+      <c r="P125" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q125" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0405</t>
+        </is>
+      </c>
+      <c r="V125" t="inlineStr">
+        <is>
+          <t>TR_S1994_95_00325</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C126" t="n">
+        <v>6</v>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Chomýž</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N126" t="inlineStr">
+        <is>
+          <t>Blansko</t>
+        </is>
+      </c>
+      <c r="O126" t="inlineStr">
+        <is>
+          <t>NODE_S1994_95_0091</t>
+        </is>
+      </c>
+      <c r="P126" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q126" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0406</t>
+        </is>
+      </c>
+      <c r="V126" t="inlineStr">
+        <is>
+          <t>TR_S1994_95_00326</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C127" t="n">
+        <v>7</v>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Kojetín</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N127" t="inlineStr">
+        <is>
+          <t>Blansko</t>
+        </is>
+      </c>
+      <c r="O127" t="inlineStr">
+        <is>
+          <t>NODE_S1994_95_0091</t>
+        </is>
+      </c>
+      <c r="P127" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q127" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0407</t>
+        </is>
+      </c>
+      <c r="V127" t="inlineStr">
+        <is>
+          <t>TR_S1994_95_00327</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C128" t="n">
+        <v>1</v>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Náměšť nad Oslavou B</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N128" t="inlineStr">
+        <is>
+          <t>Blansko</t>
+        </is>
+      </c>
+      <c r="O128" t="inlineStr">
+        <is>
+          <t>NODE_S1994_95_0091</t>
+        </is>
+      </c>
+      <c r="P128" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q128" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0408</t>
+        </is>
+      </c>
+      <c r="V128" t="inlineStr">
+        <is>
+          <t>TR_S1994_95_00328</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C129" t="n">
+        <v>2</v>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Studenec</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N129" t="inlineStr">
+        <is>
+          <t>Blansko</t>
+        </is>
+      </c>
+      <c r="O129" t="inlineStr">
+        <is>
+          <t>NODE_S1994_95_0091</t>
+        </is>
+      </c>
+      <c r="P129" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q129" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0409</t>
+        </is>
+      </c>
+      <c r="V129" t="inlineStr">
+        <is>
+          <t>TR_S1994_95_00329</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C130" t="n">
+        <v>3</v>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Stařeč</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N130" t="inlineStr">
+        <is>
+          <t>Blansko</t>
+        </is>
+      </c>
+      <c r="O130" t="inlineStr">
+        <is>
+          <t>NODE_S1994_95_0091</t>
+        </is>
+      </c>
+      <c r="P130" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q130" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0410</t>
+        </is>
+      </c>
+      <c r="V130" t="inlineStr">
+        <is>
+          <t>TR_S1994_95_00330</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C131" t="n">
+        <v>4</v>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Okříšky</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N131" t="inlineStr">
+        <is>
+          <t>Blansko</t>
+        </is>
+      </c>
+      <c r="O131" t="inlineStr">
+        <is>
+          <t>NODE_S1994_95_0091</t>
+        </is>
+      </c>
+      <c r="P131" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q131" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0411</t>
+        </is>
+      </c>
+      <c r="V131" t="inlineStr">
+        <is>
+          <t>TR_S1994_95_00331</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C132" t="n">
+        <v>5</v>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>Pokojovice</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N132" t="inlineStr">
+        <is>
+          <t>Blansko</t>
+        </is>
+      </c>
+      <c r="O132" t="inlineStr">
+        <is>
+          <t>NODE_S1994_95_0091</t>
+        </is>
+      </c>
+      <c r="P132" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q132" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0412</t>
+        </is>
+      </c>
+      <c r="V132" t="inlineStr">
+        <is>
+          <t>TR_S1994_95_00332</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C133" t="n">
+        <v>6</v>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>Moravské Budějovice</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N133" t="inlineStr">
+        <is>
+          <t>Blansko</t>
+        </is>
+      </c>
+      <c r="O133" t="inlineStr">
+        <is>
+          <t>NODE_S1994_95_0091</t>
+        </is>
+      </c>
+      <c r="P133" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q133" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0413</t>
+        </is>
+      </c>
+      <c r="V133" t="inlineStr">
+        <is>
+          <t>TR_S1994_95_00333</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C134" t="n">
+        <v>7</v>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>Vladislav</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N134" t="inlineStr">
+        <is>
+          <t>Blansko</t>
+        </is>
+      </c>
+      <c r="O134" t="inlineStr">
+        <is>
+          <t>NODE_S1994_95_0091</t>
+        </is>
+      </c>
+      <c r="P134" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q134" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0414</t>
+        </is>
+      </c>
+      <c r="V134" t="inlineStr">
+        <is>
+          <t>TR_S1994_95_00334</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C135" t="n">
+        <v>8</v>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>Mohelno</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N135" t="inlineStr">
+        <is>
+          <t>Blansko</t>
+        </is>
+      </c>
+      <c r="O135" t="inlineStr">
+        <is>
+          <t>NODE_S1994_95_0091</t>
+        </is>
+      </c>
+      <c r="P135" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q135" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0415</t>
+        </is>
+      </c>
+      <c r="V135" t="inlineStr">
+        <is>
+          <t>TR_S1994_95_00335</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C136" t="n">
+        <v>1</v>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>Vítovice</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N136" t="inlineStr">
+        <is>
+          <t>Blansko</t>
+        </is>
+      </c>
+      <c r="O136" t="inlineStr">
+        <is>
+          <t>NODE_S1994_95_0091</t>
+        </is>
+      </c>
+      <c r="P136" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q136" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0416</t>
+        </is>
+      </c>
+      <c r="V136" t="inlineStr">
+        <is>
+          <t>TR_S1994_95_00336</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C137" t="n">
+        <v>1</v>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>Želechovice</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N137" t="inlineStr">
+        <is>
+          <t>Blansko</t>
+        </is>
+      </c>
+      <c r="O137" t="inlineStr">
+        <is>
+          <t>NODE_S1994_95_0091</t>
+        </is>
+      </c>
+      <c r="P137" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q137" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0417</t>
+        </is>
+      </c>
+      <c r="V137" t="inlineStr">
+        <is>
+          <t>TR_S1994_95_00337</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C138" t="n">
+        <v>2</v>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>Z-klub Zlín</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N138" t="inlineStr">
+        <is>
+          <t>Blansko</t>
+        </is>
+      </c>
+      <c r="O138" t="inlineStr">
+        <is>
+          <t>NODE_S1994_95_0091</t>
+        </is>
+      </c>
+      <c r="P138" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q138" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0418</t>
+        </is>
+      </c>
+      <c r="V138" t="inlineStr">
+        <is>
+          <t>TR_S1994_95_00338</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C139" t="n">
+        <v>3</v>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>Technika Zlín</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N139" t="inlineStr">
+        <is>
+          <t>Blansko</t>
+        </is>
+      </c>
+      <c r="O139" t="inlineStr">
+        <is>
+          <t>NODE_S1994_95_0091</t>
+        </is>
+      </c>
+      <c r="P139" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q139" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0419</t>
+        </is>
+      </c>
+      <c r="V139" t="inlineStr">
+        <is>
+          <t>TR_S1994_95_00339</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C140" t="n">
+        <v>4</v>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>Brumov</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N140" t="inlineStr">
+        <is>
+          <t>Blansko</t>
+        </is>
+      </c>
+      <c r="O140" t="inlineStr">
+        <is>
+          <t>NODE_S1994_95_0091</t>
+        </is>
+      </c>
+      <c r="P140" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q140" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0420</t>
+        </is>
+      </c>
+      <c r="V140" t="inlineStr">
+        <is>
+          <t>TR_S1994_95_00340</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C141" t="n">
+        <v>5</v>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>Bojkovice</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N141" t="inlineStr">
+        <is>
+          <t>Blansko</t>
+        </is>
+      </c>
+      <c r="O141" t="inlineStr">
+        <is>
+          <t>NODE_S1994_95_0091</t>
+        </is>
+      </c>
+      <c r="P141" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q141" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0421</t>
+        </is>
+      </c>
+      <c r="V141" t="inlineStr">
+        <is>
+          <t>TR_S1994_95_00341</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C142" t="n">
+        <v>1</v>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>Znojmo B</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N142" t="inlineStr">
+        <is>
+          <t>Blansko</t>
+        </is>
+      </c>
+      <c r="O142" t="inlineStr">
+        <is>
+          <t>NODE_S1994_95_0091</t>
+        </is>
+      </c>
+      <c r="P142" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q142" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0422</t>
+        </is>
+      </c>
+      <c r="V142" t="inlineStr">
+        <is>
+          <t>TR_S1994_95_00342</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C143" t="n">
+        <v>2</v>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>Citovice</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N143" t="inlineStr">
+        <is>
+          <t>Blansko</t>
+        </is>
+      </c>
+      <c r="O143" t="inlineStr">
+        <is>
+          <t>NODE_S1994_95_0091</t>
+        </is>
+      </c>
+      <c r="P143" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q143" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0423</t>
+        </is>
+      </c>
+      <c r="V143" t="inlineStr">
+        <is>
+          <t>TR_S1994_95_00343</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C144" t="n">
+        <v>3</v>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>Blížkovice</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N144" t="inlineStr">
+        <is>
+          <t>Blansko</t>
+        </is>
+      </c>
+      <c r="O144" t="inlineStr">
+        <is>
+          <t>NODE_S1994_95_0091</t>
+        </is>
+      </c>
+      <c r="P144" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q144" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0424</t>
+        </is>
+      </c>
+      <c r="V144" t="inlineStr">
+        <is>
+          <t>TR_S1994_95_00344</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C145" t="n">
+        <v>4</v>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>Pavlice</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N145" t="inlineStr">
+        <is>
+          <t>Blansko</t>
+        </is>
+      </c>
+      <c r="O145" t="inlineStr">
+        <is>
+          <t>NODE_S1994_95_0091</t>
+        </is>
+      </c>
+      <c r="P145" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q145" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0425</t>
+        </is>
+      </c>
+      <c r="V145" t="inlineStr">
+        <is>
+          <t>TR_S1994_95_00345</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C146" t="n">
+        <v>5</v>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>Horní Dunajovice</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N146" t="inlineStr">
+        <is>
+          <t>Blansko</t>
+        </is>
+      </c>
+      <c r="O146" t="inlineStr">
+        <is>
+          <t>NODE_S1994_95_0091</t>
+        </is>
+      </c>
+      <c r="P146" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q146" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0426</t>
+        </is>
+      </c>
+      <c r="V146" t="inlineStr">
+        <is>
+          <t>TR_S1994_95_00346</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C147" t="n">
+        <v>1</v>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>Vír</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N147" t="inlineStr">
+        <is>
+          <t>Blansko</t>
+        </is>
+      </c>
+      <c r="O147" t="inlineStr">
+        <is>
+          <t>NODE_S1994_95_0091</t>
+        </is>
+      </c>
+      <c r="P147" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q147" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0427</t>
+        </is>
+      </c>
+      <c r="V147" t="inlineStr">
+        <is>
+          <t>TR_S1994_95_00347</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C148" t="n">
+        <v>2</v>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>MIKO Žďár nad Sázavou</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N148" t="inlineStr">
+        <is>
+          <t>Blansko</t>
+        </is>
+      </c>
+      <c r="O148" t="inlineStr">
+        <is>
+          <t>NODE_S1994_95_0091</t>
+        </is>
+      </c>
+      <c r="P148" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q148" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0428</t>
+        </is>
+      </c>
+      <c r="V148" t="inlineStr">
+        <is>
+          <t>TR_S1994_95_00348</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C149" t="n">
+        <v>3</v>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>Šakals Žďár nad Sázavou</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N149" t="inlineStr">
+        <is>
+          <t>Blansko</t>
+        </is>
+      </c>
+      <c r="O149" t="inlineStr">
+        <is>
+          <t>NODE_S1994_95_0091</t>
+        </is>
+      </c>
+      <c r="P149" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q149" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0429</t>
+        </is>
+      </c>
+      <c r="V149" t="inlineStr">
+        <is>
+          <t>TR_S1994_95_00349</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C150" t="n">
+        <v>4</v>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>Vojnův Městec</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N150" t="inlineStr">
+        <is>
+          <t>Blansko</t>
+        </is>
+      </c>
+      <c r="O150" t="inlineStr">
+        <is>
+          <t>NODE_S1994_95_0091</t>
+        </is>
+      </c>
+      <c r="P150" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q150" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0430</t>
+        </is>
+      </c>
+      <c r="V150" t="inlineStr">
+        <is>
+          <t>TR_S1994_95_00350</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C151" t="n">
+        <v>5</v>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>Slavkovice</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N151" t="inlineStr">
+        <is>
+          <t>Blansko</t>
+        </is>
+      </c>
+      <c r="O151" t="inlineStr">
+        <is>
+          <t>NODE_S1994_95_0091</t>
+        </is>
+      </c>
+      <c r="P151" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q151" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0431</t>
+        </is>
+      </c>
+      <c r="V151" t="inlineStr">
+        <is>
+          <t>TR_S1994_95_00351</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C152" t="n">
+        <v>6</v>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>Měřín</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N152" t="inlineStr">
+        <is>
+          <t>Blansko</t>
+        </is>
+      </c>
+      <c r="O152" t="inlineStr">
+        <is>
+          <t>NODE_S1994_95_0091</t>
+        </is>
+      </c>
+      <c r="P152" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q152" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0432</t>
+        </is>
+      </c>
+      <c r="V152" t="inlineStr">
+        <is>
+          <t>TR_S1994_95_00352</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C153" t="n">
+        <v>7</v>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>Křižanov</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N153" t="inlineStr">
+        <is>
+          <t>Blansko</t>
+        </is>
+      </c>
+      <c r="O153" t="inlineStr">
+        <is>
+          <t>NODE_S1994_95_0091</t>
+        </is>
+      </c>
+      <c r="P153" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q153" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0433</t>
+        </is>
+      </c>
+      <c r="V153" t="inlineStr">
+        <is>
+          <t>TR_S1994_95_00353</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C154" t="n">
+        <v>8</v>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>Velké Meziříčí B</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N154" t="inlineStr">
+        <is>
+          <t>Blansko</t>
+        </is>
+      </c>
+      <c r="O154" t="inlineStr">
+        <is>
+          <t>NODE_S1994_95_0091</t>
+        </is>
+      </c>
+      <c r="P154" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q154" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0434</t>
+        </is>
+      </c>
+      <c r="V154" t="inlineStr">
+        <is>
+          <t>TR_S1994_95_00354</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -12527,7 +15263,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W35"/>
+  <dimension ref="A1:W37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -15065,6 +17801,73 @@
         </is>
       </c>
     </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>KP I.třídy</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>NODE_S1994_95_0092</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>5</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Poruba</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>KP I.třídy</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>NODE_S1994_95_0092</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0435</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>TR_S1994_95_00355</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -15458,7 +18261,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N101"/>
+  <dimension ref="A1:N107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19915,6 +22718,228 @@
       <c r="A101" t="inlineStr">
         <is>
           <t>II.liga: 2 skupiny.</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>NODE_S1994_95_0087</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Středočeský – Beroun</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>league</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>REG_STC</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>NODE_S1994_95_0037</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy).</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>NODE_S1994_95_0088</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Jihočeský – Č.Budějovice + Č.Krumlov</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>league</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>REG_JHC</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>NODE_S1994_95_0041</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy).</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>NODE_S1994_95_0089</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Východočeský – Havlíčkův Brod</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>league</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>REG_VYC</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>NODE_S1994_95_0056</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy).</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>NODE_S1994_95_0090</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Jihomoravský – KP I.třídy</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>league</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>REG_JHM</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>NODE_S1994_95_0066</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy).</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>NODE_S1994_95_0091</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Jihomoravský – Blansko</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>league</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>REG_JHM</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>NODE_S1994_95_0066</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy).</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>NODE_S1994_95_0092</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Severomoravský – KP I.třídy</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>league</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>REG_SVM</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>NODE_S1994_95_0080</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy).</t>
         </is>
       </c>
     </row>
@@ -22040,7 +25065,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J311"/>
+  <dimension ref="A1:J423"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="10" max="10"/>
@@ -35795,6 +38820,3650 @@
       <c r="J311" t="inlineStr">
         <is>
           <t>BD Opava</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0324</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>Dynastav Beroun</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>Dynastav Beroun</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>30STRC</t>
+        </is>
+      </c>
+      <c r="F312" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I312" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0325</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>Jiskra Zruč nad Sázavou</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>Jiskra Zruč nad Sázavou</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>30STRC</t>
+        </is>
+      </c>
+      <c r="F313" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I313" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0326</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>Chicago Úmonín</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>Chicago Úmonín</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>30STRC</t>
+        </is>
+      </c>
+      <c r="F314" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I314" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0327</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>Sokol Řendějov</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>Sokol Řendějov</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>30STRC</t>
+        </is>
+      </c>
+      <c r="F315" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I315" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0328</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>Stadion Kutná Hora B</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>Stadion Kutná Hora B</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>30STRC</t>
+        </is>
+      </c>
+      <c r="F316" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I316" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0329</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>Slavia Vinaře</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>Slavia Vinaře</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>30STRC</t>
+        </is>
+      </c>
+      <c r="F317" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I317" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0330</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>Sokol Uhl.Janovice</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>Sokol Uhl.Janovice</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>30STRC</t>
+        </is>
+      </c>
+      <c r="F318" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I318" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0331</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>Slavoj Čáslav</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>Slavoj Čáslav</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>30STRC</t>
+        </is>
+      </c>
+      <c r="F319" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I319" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0332</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>Kablo Kolín</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>Kablo Kolín</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>30STRC</t>
+        </is>
+      </c>
+      <c r="F320" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I320" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0333</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>Koramo Kolín</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>Koramo Kolín</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>30STRC</t>
+        </is>
+      </c>
+      <c r="F321" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I321" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0334</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>Sokol Žabonosy</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>Sokol Žabonosy</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>30STRC</t>
+        </is>
+      </c>
+      <c r="F322" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I322" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0335</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>OTK Kolín</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>OTK Kolín</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>30STRC</t>
+        </is>
+      </c>
+      <c r="F323" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I323" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0336</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>Strojírny Kolín</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>Strojírny Kolín</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>30STRC</t>
+        </is>
+      </c>
+      <c r="F324" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I324" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0337</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>Sokol Žilina</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>Sokol Žilina</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>30STRC</t>
+        </is>
+      </c>
+      <c r="F325" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I325" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0338</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>HC Zlonice</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>HC Zlonice</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>30STRC</t>
+        </is>
+      </c>
+      <c r="F326" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I326" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0339</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>Masokombinát Kladno</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>Masokombinát Kladno</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>30STRC</t>
+        </is>
+      </c>
+      <c r="F327" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I327" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0340</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>Sokol Braškov</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>Sokol Braškov</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>30STRC</t>
+        </is>
+      </c>
+      <c r="F328" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I328" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0341</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>Doly Kladno</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>Doly Kladno</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>30STRC</t>
+        </is>
+      </c>
+      <c r="F329" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I329" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0342</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>Hvězda Kladno B</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>Hvězda Kladno B</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>30STRC</t>
+        </is>
+      </c>
+      <c r="F330" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I330" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0343</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>Spartak Hospozín</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>Spartak Hospozín</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>30STRC</t>
+        </is>
+      </c>
+      <c r="F331" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I331" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0344</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>HC Lány</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>HC Lány</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>30STRC</t>
+        </is>
+      </c>
+      <c r="F332" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I332" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0345</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>HC Nové Strašecí</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>HC Nové Strašecí</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>30STRC</t>
+        </is>
+      </c>
+      <c r="F333" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I333" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0346</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>HC Kněževes</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>HC Kněževes</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>30STRC</t>
+        </is>
+      </c>
+      <c r="F334" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I334" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0347</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>Sokol Sýkořice</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>Sokol Sýkořice</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>30STRC</t>
+        </is>
+      </c>
+      <c r="F335" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I335" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0348</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>HC Hořesedly</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>HC Hořesedly</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>30STRC</t>
+        </is>
+      </c>
+      <c r="F336" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I336" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0349</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>HC Kralovice</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>HC Kralovice</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>30STRC</t>
+        </is>
+      </c>
+      <c r="F337" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I337" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0350</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>Baník Rynholec</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>Baník Rynholec</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>30STRC</t>
+        </is>
+      </c>
+      <c r="F338" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I338" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0351</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>Řevnice „B“</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>Řevnice „B“</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>30STRC</t>
+        </is>
+      </c>
+      <c r="F339" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I339" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0352</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>HC Roudnice nad Labem</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>HC Roudnice nad Labem</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>30STRC</t>
+        </is>
+      </c>
+      <c r="F340" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I340" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0353</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>finále</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>finále</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>30STRC</t>
+        </is>
+      </c>
+      <c r="F341" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I341" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0354</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>SD-CHO 6:6,4:6</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>SD-CHO 6:6,4:6</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>30STRC</t>
+        </is>
+      </c>
+      <c r="F342" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I342" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0355</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>finále: Dvůr-Týniště 7:2</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>finále: Dvůr-Týniště 7:2</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>30STRC</t>
+        </is>
+      </c>
+      <c r="F343" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I343" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0356</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>Sokol Jindřichův Hradec</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>Sokol Jindřichův Hradec</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>30JHCK</t>
+        </is>
+      </c>
+      <c r="F344" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I344" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0357</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>Kardašova Řečice</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>Kardašova Řečice</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>30JHCK</t>
+        </is>
+      </c>
+      <c r="F345" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I345" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0358</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>Jitka Jindřichův Hradec</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>Jitka Jindřichův Hradec</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>30JHCK</t>
+        </is>
+      </c>
+      <c r="F346" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I346" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0359</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>Stranná / Žirovnice</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>Stranná / Žirovnice</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>30JHCK</t>
+        </is>
+      </c>
+      <c r="F347" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I347" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0360</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>Sokol Velká Radouň B</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>Sokol Velká Radouň B</t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>30JHCK</t>
+        </is>
+      </c>
+      <c r="F348" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I348" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0361</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>Nová Včelnice</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>Nová Včelnice</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>30JHCK</t>
+        </is>
+      </c>
+      <c r="F349" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I349" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0362</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>ŠS Humpolec</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>ŠS Humpolec</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>30JHCK</t>
+        </is>
+      </c>
+      <c r="F350" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I350" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0363</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>Jiskra Humpolec</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>Jiskra Humpolec</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>30JHCK</t>
+        </is>
+      </c>
+      <c r="F351" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I351" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0364</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>Lipice</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>Lipice</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>30JHCK</t>
+        </is>
+      </c>
+      <c r="F352" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I352" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0365</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>Horní Cerekev</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>Horní Cerekev</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>30JHCK</t>
+        </is>
+      </c>
+      <c r="F353" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I353" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0366</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>HC Pelhřimov</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>HC Pelhřimov</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>30JHCK</t>
+        </is>
+      </c>
+      <c r="F354" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I354" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0367</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>Košetice</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>Košetice</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>30JHCK</t>
+        </is>
+      </c>
+      <c r="F355" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I355" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0368</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>Záboří</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>Záboří</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>30JHCK</t>
+        </is>
+      </c>
+      <c r="F356" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I356" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0369</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>Cehnice</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>Cehnice</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>30JHCK</t>
+        </is>
+      </c>
+      <c r="F357" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I357" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0370</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>UniElektro</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>UniElektro</t>
+        </is>
+      </c>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>30JHCK</t>
+        </is>
+      </c>
+      <c r="F358" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I358" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0371</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>Horažďovice</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>Horažďovice</t>
+        </is>
+      </c>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>30JHCK</t>
+        </is>
+      </c>
+      <c r="F359" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I359" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0372</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>TJ Sokol Katovice B</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>TJ Sokol Katovice B</t>
+        </is>
+      </c>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>30JHCK</t>
+        </is>
+      </c>
+      <c r="F360" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I360" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0373</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>Radomyšl</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>Radomyšl</t>
+        </is>
+      </c>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>30JHCK</t>
+        </is>
+      </c>
+      <c r="F361" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I361" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0374</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>Volyně</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>Volyně</t>
+        </is>
+      </c>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>30JHCK</t>
+        </is>
+      </c>
+      <c r="F362" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I362" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0375</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>Drahonice</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>Drahonice</t>
+        </is>
+      </c>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>30JHCK</t>
+        </is>
+      </c>
+      <c r="F363" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I363" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0376</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>Přešťovice</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>Přešťovice</t>
+        </is>
+      </c>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>30JHCK</t>
+        </is>
+      </c>
+      <c r="F364" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I364" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0377</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>Nekoř</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>Nekoř</t>
+        </is>
+      </c>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>30VYCH</t>
+        </is>
+      </c>
+      <c r="F365" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I365" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0378</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>Třebovice</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>Třebovice</t>
+        </is>
+      </c>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>30VYCH</t>
+        </is>
+      </c>
+      <c r="F366" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I366" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0379</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>Česká Třebová</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>Česká Třebová</t>
+        </is>
+      </c>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>30VYCH</t>
+        </is>
+      </c>
+      <c r="F367" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I367" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0380</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>Dlouhoňovice</t>
+        </is>
+      </c>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>Dlouhoňovice</t>
+        </is>
+      </c>
+      <c r="D368" t="inlineStr">
+        <is>
+          <t>30VYCH</t>
+        </is>
+      </c>
+      <c r="F368" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I368" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0381</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>Králíky</t>
+        </is>
+      </c>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>Králíky</t>
+        </is>
+      </c>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>30VYCH</t>
+        </is>
+      </c>
+      <c r="F369" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I369" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0382</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>Lanškroun</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>Lanškroun</t>
+        </is>
+      </c>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>30VYCH</t>
+        </is>
+      </c>
+      <c r="F370" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I370" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0383</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>Voděrady</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>Voděrady</t>
+        </is>
+      </c>
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>30VYCH</t>
+        </is>
+      </c>
+      <c r="F371" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I371" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0384</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>Řetová</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>Řetová</t>
+        </is>
+      </c>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>30VYCH</t>
+        </is>
+      </c>
+      <c r="F372" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I372" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0385</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>Malhostovice</t>
+        </is>
+      </c>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>Malhostovice</t>
+        </is>
+      </c>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>30JHMR</t>
+        </is>
+      </c>
+      <c r="F373" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I373" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0386</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>Sloup</t>
+        </is>
+      </c>
+      <c r="C374" t="inlineStr">
+        <is>
+          <t>Sloup</t>
+        </is>
+      </c>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t>30JHMR</t>
+        </is>
+      </c>
+      <c r="E374" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="F374" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I374" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0387</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>Bořitov</t>
+        </is>
+      </c>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>Bořitov</t>
+        </is>
+      </c>
+      <c r="D375" t="inlineStr">
+        <is>
+          <t>30JHMR</t>
+        </is>
+      </c>
+      <c r="F375" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I375" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0388</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>Vilémovice</t>
+        </is>
+      </c>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>Vilémovice</t>
+        </is>
+      </c>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>30JHMR</t>
+        </is>
+      </c>
+      <c r="E376" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="F376" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I376" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0389</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>Kunštát</t>
+        </is>
+      </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>Kunštát</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>30JHMR</t>
+        </is>
+      </c>
+      <c r="F377" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I377" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0390</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>Technika Brno</t>
+        </is>
+      </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>Technika Brno</t>
+        </is>
+      </c>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>30JHMR</t>
+        </is>
+      </c>
+      <c r="F378" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I378" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0391</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>Hrušky B</t>
+        </is>
+      </c>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>Hrušky B</t>
+        </is>
+      </c>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>30JHMR</t>
+        </is>
+      </c>
+      <c r="E379" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F379" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I379" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0392</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>Šerkovice</t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>Šerkovice</t>
+        </is>
+      </c>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>30JHMR</t>
+        </is>
+      </c>
+      <c r="E380" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="F380" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I380" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0393</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>Lelekovice</t>
+        </is>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>Lelekovice</t>
+        </is>
+      </c>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>30JHMR</t>
+        </is>
+      </c>
+      <c r="F381" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I381" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0394</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>Oslavany</t>
+        </is>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>Oslavany</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>30JHMR</t>
+        </is>
+      </c>
+      <c r="F382" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I382" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0395</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>Starý Lískovec</t>
+        </is>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>Starý Lískovec</t>
+        </is>
+      </c>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>30JHMR</t>
+        </is>
+      </c>
+      <c r="F383" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I383" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0396</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>Dačice</t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>Dačice</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>30JHMR</t>
+        </is>
+      </c>
+      <c r="F384" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I384" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0397</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>Polná</t>
+        </is>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>Polná</t>
+        </is>
+      </c>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>30JHMR</t>
+        </is>
+      </c>
+      <c r="F385" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I385" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0398</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>Růžená</t>
+        </is>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>Růžená</t>
+        </is>
+      </c>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>30JHMR</t>
+        </is>
+      </c>
+      <c r="E386" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="F386" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I386" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0399</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>Puklice</t>
+        </is>
+      </c>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>Puklice</t>
+        </is>
+      </c>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>30JHMR</t>
+        </is>
+      </c>
+      <c r="F387" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I387" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0400</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>Brtnice</t>
+        </is>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>Brtnice</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>30JHMR</t>
+        </is>
+      </c>
+      <c r="F388" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I388" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0401</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>SKP Kroměříž</t>
+        </is>
+      </c>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>SKP Kroměříž</t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>30JHMR</t>
+        </is>
+      </c>
+      <c r="F389" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I389" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0402</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>Milenov</t>
+        </is>
+      </c>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>Milenov</t>
+        </is>
+      </c>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>30JHMR</t>
+        </is>
+      </c>
+      <c r="F390" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I390" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0403</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>Zborovice</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>Zborovice</t>
+        </is>
+      </c>
+      <c r="D391" t="inlineStr">
+        <is>
+          <t>30JHMR</t>
+        </is>
+      </c>
+      <c r="F391" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I391" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0404</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>Troubky</t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>Troubky</t>
+        </is>
+      </c>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>30JHMR</t>
+        </is>
+      </c>
+      <c r="F392" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I392" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0405</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>Citov</t>
+        </is>
+      </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>Citov</t>
+        </is>
+      </c>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>30JHMR</t>
+        </is>
+      </c>
+      <c r="F393" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I393" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0406</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>Chomýž</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>Chomýž</t>
+        </is>
+      </c>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>30JHMR</t>
+        </is>
+      </c>
+      <c r="F394" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I394" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0407</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>Kojetín</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>Kojetín</t>
+        </is>
+      </c>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>30JHMR</t>
+        </is>
+      </c>
+      <c r="F395" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I395" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0408</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>Náměšť nad Oslavou B</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>Náměšť nad Oslavou B</t>
+        </is>
+      </c>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>30JHMR</t>
+        </is>
+      </c>
+      <c r="E396" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F396" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I396" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0409</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>Studenec</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>Studenec</t>
+        </is>
+      </c>
+      <c r="D397" t="inlineStr">
+        <is>
+          <t>30JHMR</t>
+        </is>
+      </c>
+      <c r="F397" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I397" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0410</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>Stařeč</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>Stařeč</t>
+        </is>
+      </c>
+      <c r="D398" t="inlineStr">
+        <is>
+          <t>30JHMR</t>
+        </is>
+      </c>
+      <c r="F398" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I398" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0411</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>Okříšky</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>Okříšky</t>
+        </is>
+      </c>
+      <c r="D399" t="inlineStr">
+        <is>
+          <t>30JHMR</t>
+        </is>
+      </c>
+      <c r="F399" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I399" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0412</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>Pokojovice</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>Pokojovice</t>
+        </is>
+      </c>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>30JHMR</t>
+        </is>
+      </c>
+      <c r="F400" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I400" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0413</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>Moravské Budějovice</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>Moravské Budějovice</t>
+        </is>
+      </c>
+      <c r="D401" t="inlineStr">
+        <is>
+          <t>30JHMR</t>
+        </is>
+      </c>
+      <c r="F401" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I401" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0414</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>Vladislav</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>Vladislav</t>
+        </is>
+      </c>
+      <c r="D402" t="inlineStr">
+        <is>
+          <t>30JHMR</t>
+        </is>
+      </c>
+      <c r="F402" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I402" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0415</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>Mohelno</t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>Mohelno</t>
+        </is>
+      </c>
+      <c r="D403" t="inlineStr">
+        <is>
+          <t>30JHMR</t>
+        </is>
+      </c>
+      <c r="F403" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I403" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0416</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>Vítovice</t>
+        </is>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>Vítovice</t>
+        </is>
+      </c>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>30JHMR</t>
+        </is>
+      </c>
+      <c r="F404" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I404" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0417</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>Želechovice</t>
+        </is>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>Želechovice</t>
+        </is>
+      </c>
+      <c r="D405" t="inlineStr">
+        <is>
+          <t>30JHMR</t>
+        </is>
+      </c>
+      <c r="E405" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="F405" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I405" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0418</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>Z-klub Zlín</t>
+        </is>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>Z-klub Zlín</t>
+        </is>
+      </c>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>30JHMR</t>
+        </is>
+      </c>
+      <c r="F406" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I406" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0419</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>Technika Zlín</t>
+        </is>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>Technika Zlín</t>
+        </is>
+      </c>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>30JHMR</t>
+        </is>
+      </c>
+      <c r="F407" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I407" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0420</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>Brumov</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>Brumov</t>
+        </is>
+      </c>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>30JHMR</t>
+        </is>
+      </c>
+      <c r="F408" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I408" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0421</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>Bojkovice</t>
+        </is>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>Bojkovice</t>
+        </is>
+      </c>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>30JHMR</t>
+        </is>
+      </c>
+      <c r="F409" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I409" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0422</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>Znojmo B</t>
+        </is>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>Znojmo B</t>
+        </is>
+      </c>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>30JHMR</t>
+        </is>
+      </c>
+      <c r="F410" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I410" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0423</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>Citovice</t>
+        </is>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>Citovice</t>
+        </is>
+      </c>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>30JHMR</t>
+        </is>
+      </c>
+      <c r="F411" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I411" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0424</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>Blížkovice</t>
+        </is>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>Blížkovice</t>
+        </is>
+      </c>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>30JHMR</t>
+        </is>
+      </c>
+      <c r="F412" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I412" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0425</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>Pavlice</t>
+        </is>
+      </c>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>Pavlice</t>
+        </is>
+      </c>
+      <c r="D413" t="inlineStr">
+        <is>
+          <t>30JHMR</t>
+        </is>
+      </c>
+      <c r="F413" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I413" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0426</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>Horní Dunajovice</t>
+        </is>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>Horní Dunajovice</t>
+        </is>
+      </c>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>30JHMR</t>
+        </is>
+      </c>
+      <c r="F414" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I414" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0427</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>Vír</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>Vír</t>
+        </is>
+      </c>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>30JHMR</t>
+        </is>
+      </c>
+      <c r="F415" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I415" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0428</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>MIKO Žďár nad Sázavou</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>MIKO Žďár nad Sázavou</t>
+        </is>
+      </c>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>30JHMR</t>
+        </is>
+      </c>
+      <c r="E416" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F416" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I416" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0429</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>Šakals Žďár nad Sázavou</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>Šakals Žďár nad Sázavou</t>
+        </is>
+      </c>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>30JHMR</t>
+        </is>
+      </c>
+      <c r="E417" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F417" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I417" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0430</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>Vojnův Městec</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>Vojnův Městec</t>
+        </is>
+      </c>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>30JHMR</t>
+        </is>
+      </c>
+      <c r="F418" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I418" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0431</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>Slavkovice</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>Slavkovice</t>
+        </is>
+      </c>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>30JHMR</t>
+        </is>
+      </c>
+      <c r="E419" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F419" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I419" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0432</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>Měřín</t>
+        </is>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>Měřín</t>
+        </is>
+      </c>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>30JHMR</t>
+        </is>
+      </c>
+      <c r="F420" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I420" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0433</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>Křižanov</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>Křižanov</t>
+        </is>
+      </c>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>30JHMR</t>
+        </is>
+      </c>
+      <c r="E421" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="F421" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I421" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0434</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>Velké Meziříčí B</t>
+        </is>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>Velké Meziříčí B</t>
+        </is>
+      </c>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>30JHMR</t>
+        </is>
+      </c>
+      <c r="E422" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F422" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I422" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0435</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>Poruba</t>
+        </is>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>Poruba</t>
+        </is>
+      </c>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>30SVMR</t>
+        </is>
+      </c>
+      <c r="F423" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I423" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
         </is>
       </c>
     </row>
@@ -43344,7 +50013,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W47"/>
+  <dimension ref="A1:W80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -46059,6 +52728,1444 @@
         </is>
       </c>
     </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Beroun</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>NODE_S1994_95_0087</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>1</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Dynastav Beroun</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>Beroun</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>NODE_S1994_95_0087</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0324</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>TR_S1994_95_00244</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>1</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Jiskra Zruč nad Sázavou</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>Beroun</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>NODE_S1994_95_0087</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0325</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>TR_S1994_95_00245</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>2</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Chicago Úmonín</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>Beroun</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>NODE_S1994_95_0087</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0326</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>TR_S1994_95_00246</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>3</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Sokol Řendějov</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>Beroun</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>NODE_S1994_95_0087</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0327</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>TR_S1994_95_00247</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>4</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Stadion Kutná Hora B</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>Beroun</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>NODE_S1994_95_0087</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0328</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>TR_S1994_95_00248</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>5</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Slavia Vinaře</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>Beroun</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>NODE_S1994_95_0087</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0329</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>TR_S1994_95_00249</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>6</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Sokol Uhl.Janovice</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>Beroun</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>NODE_S1994_95_0087</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0330</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>TR_S1994_95_00250</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>7</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Slavoj Čáslav</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>Beroun</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>NODE_S1994_95_0087</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0331</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>TR_S1994_95_00251</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Kablo Kolín</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>Beroun</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>NODE_S1994_95_0087</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0332</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>TR_S1994_95_00252</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Koramo Kolín</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>Beroun</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>NODE_S1994_95_0087</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0333</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>TR_S1994_95_00253</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>3</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Sokol Žabonosy</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>Beroun</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>NODE_S1994_95_0087</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0334</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>TR_S1994_95_00254</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>OTK Kolín</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>Beroun</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>NODE_S1994_95_0087</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0335</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>TR_S1994_95_00255</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Strojírny Kolín</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>Beroun</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>NODE_S1994_95_0087</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0336</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>TR_S1994_95_00256</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>1</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Sokol Žilina</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>Beroun</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>NODE_S1994_95_0087</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0337</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>TR_S1994_95_00257</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>2</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>HC Zlonice</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>Beroun</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>NODE_S1994_95_0087</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0338</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>TR_S1994_95_00258</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>3</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Masokombinát Kladno</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>Beroun</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>NODE_S1994_95_0087</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0339</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>TR_S1994_95_00259</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>4</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Sokol Braškov</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>Beroun</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>NODE_S1994_95_0087</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0340</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>TR_S1994_95_00260</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>5</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Doly Kladno</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>Beroun</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>NODE_S1994_95_0087</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0341</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>TR_S1994_95_00261</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>6</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Hvězda Kladno B</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>Beroun</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>NODE_S1994_95_0087</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0342</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>TR_S1994_95_00262</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>7</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Spartak Hospozín</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>Beroun</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>NODE_S1994_95_0087</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q68" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0343</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>TR_S1994_95_00263</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>1</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>HC Lány</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>Beroun</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>NODE_S1994_95_0087</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0344</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>TR_S1994_95_00264</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>2</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>HC Nové Strašecí</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>Beroun</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>NODE_S1994_95_0087</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0345</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>TR_S1994_95_00265</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>3</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>HC Kněževes</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>Beroun</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>NODE_S1994_95_0087</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q71" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0346</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>TR_S1994_95_00266</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>4</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Sokol Sýkořice</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>Beroun</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>NODE_S1994_95_0087</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0347</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>TR_S1994_95_00267</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>5</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>HC Hořesedly</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>Beroun</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>NODE_S1994_95_0087</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0348</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>TR_S1994_95_00268</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>6</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>HC Kralovice</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>Beroun</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>NODE_S1994_95_0087</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q74" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0349</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>TR_S1994_95_00269</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>7</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Baník Rynholec</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>Beroun</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>NODE_S1994_95_0087</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q75" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0350</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>TR_S1994_95_00270</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>1</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Řevnice „B“</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>Beroun</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>NODE_S1994_95_0087</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q76" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0351</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>TR_S1994_95_00271</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>HC Roudnice nad Labem</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>Beroun</t>
+        </is>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>NODE_S1994_95_0087</t>
+        </is>
+      </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q77" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0352</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>TR_S1994_95_00272</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>finále</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>Beroun</t>
+        </is>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>NODE_S1994_95_0087</t>
+        </is>
+      </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q78" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0353</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>TR_S1994_95_00273</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>SD-CHO 6:6,4:6</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>Beroun</t>
+        </is>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>NODE_S1994_95_0087</t>
+        </is>
+      </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q79" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0354</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>TR_S1994_95_00274</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>finále: Dvůr-Týniště 7:2</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>Beroun</t>
+        </is>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>NODE_S1994_95_0087</t>
+        </is>
+      </c>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q80" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0355</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>TR_S1994_95_00275</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -46070,7 +54177,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W53"/>
+  <dimension ref="A1:W75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -49456,6 +57563,955 @@
       <c r="W53" s="3" t="inlineStr">
         <is>
           <t>Strakonice</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Č.Budějovice + Č.Krumlov</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>NODE_S1994_95_0088</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Sokol Jindřichův Hradec</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>Č.Budějovice + Č.Krumlov</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>NODE_S1994_95_0088</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0356</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>TR_S1994_95_00276</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Kardašova Řečice</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>Č.Budějovice + Č.Krumlov</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>NODE_S1994_95_0088</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0357</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>TR_S1994_95_00277</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Jitka Jindřichův Hradec</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>Č.Budějovice + Č.Krumlov</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>NODE_S1994_95_0088</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0358</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>TR_S1994_95_00278</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Stranná / Žirovnice</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>Č.Budějovice + Č.Krumlov</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>NODE_S1994_95_0088</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0359</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>TR_S1994_95_00279</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Sokol Velká Radouň B</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>Č.Budějovice + Č.Krumlov</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>NODE_S1994_95_0088</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0360</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>TR_S1994_95_00280</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Nová Včelnice</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>Č.Budějovice + Č.Krumlov</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>NODE_S1994_95_0088</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0361</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>TR_S1994_95_00281</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>1</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>ŠS Humpolec</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>Č.Budějovice + Č.Krumlov</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>NODE_S1994_95_0088</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0362</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>TR_S1994_95_00282</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>2</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Jiskra Humpolec</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>Č.Budějovice + Č.Krumlov</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>NODE_S1994_95_0088</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0363</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>TR_S1994_95_00283</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>3</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Lipice</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>Č.Budějovice + Č.Krumlov</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>NODE_S1994_95_0088</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0364</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>TR_S1994_95_00284</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>4</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Horní Cerekev</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>Č.Budějovice + Č.Krumlov</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>NODE_S1994_95_0088</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0365</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>TR_S1994_95_00285</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>5</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>HC Pelhřimov</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>Č.Budějovice + Č.Krumlov</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>NODE_S1994_95_0088</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0366</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>TR_S1994_95_00286</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>6</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Košetice</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>Č.Budějovice + Č.Krumlov</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>NODE_S1994_95_0088</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0367</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>TR_S1994_95_00287</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>1</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Záboří</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>Č.Budějovice + Č.Krumlov</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>NODE_S1994_95_0088</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0368</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>TR_S1994_95_00288</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>2</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Cehnice</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>Č.Budějovice + Č.Krumlov</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>NODE_S1994_95_0088</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q68" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0369</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>TR_S1994_95_00289</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>3</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>UniElektro</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>Č.Budějovice + Č.Krumlov</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>NODE_S1994_95_0088</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0370</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>TR_S1994_95_00290</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>4</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Horažďovice</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>Č.Budějovice + Č.Krumlov</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>NODE_S1994_95_0088</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0371</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>TR_S1994_95_00291</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>5</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>TJ Sokol Katovice B</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>Č.Budějovice + Č.Krumlov</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>NODE_S1994_95_0088</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q71" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0372</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>TR_S1994_95_00292</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>6</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Radomyšl</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>Č.Budějovice + Č.Krumlov</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>NODE_S1994_95_0088</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0373</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>TR_S1994_95_00293</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>7</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Volyně</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>Č.Budějovice + Č.Krumlov</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>NODE_S1994_95_0088</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0374</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>TR_S1994_95_00294</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>8</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Drahonice</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>Č.Budějovice + Č.Krumlov</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>NODE_S1994_95_0088</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q74" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0375</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>TR_S1994_95_00295</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>9</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Přešťovice</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>Č.Budějovice + Č.Krumlov</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>NODE_S1994_95_0088</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q75" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0376</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>TR_S1994_95_00296</t>
         </is>
       </c>
     </row>

--- a/data/S1994_95_FINAL.xlsx
+++ b/data/S1994_95_FINAL.xlsx
@@ -36,7 +36,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -55,8 +55,12 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00B45309"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -83,6 +87,11 @@
         <fgColor rgb="00305496"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFE0B2"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -96,7 +105,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -108,6 +117,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -22561,8 +22572,6 @@
         <v>5</v>
       </c>
     </row>
-    <row r="88"/>
-    <row r="89"/>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
@@ -22692,7 +22701,6 @@
         </is>
       </c>
     </row>
-    <row r="97"/>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
@@ -42768,7 +42776,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F28"/>
+  <dimension ref="A1:F32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -42825,7 +42833,7 @@
           <t>CLUB_S1994_95_0014</t>
         </is>
       </c>
-      <c r="D2" s="6" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -42845,7 +42853,7 @@
           <t>CLUB_S1994_95_0015</t>
         </is>
       </c>
-      <c r="D3" s="6" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -42865,7 +42873,7 @@
           <t>CLUB_S1994_95_0021</t>
         </is>
       </c>
-      <c r="D4" s="6" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -42885,7 +42893,7 @@
           <t>CLUB_S1994_95_0032</t>
         </is>
       </c>
-      <c r="D5" s="6" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
         </is>
@@ -42905,7 +42913,7 @@
           <t>CLUB_S1994_95_0035</t>
         </is>
       </c>
-      <c r="D6" s="6" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
         </is>
@@ -42925,7 +42933,7 @@
           <t>CLUB_S1994_95_0039</t>
         </is>
       </c>
-      <c r="D7" s="6" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
         </is>
@@ -42945,7 +42953,7 @@
           <t>CLUB_S1994_95_0049</t>
         </is>
       </c>
-      <c r="D8" s="6" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>TBD: city 'KLH VT VTJ Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -42965,7 +42973,7 @@
           <t>CLUB_S1994_95_0070</t>
         </is>
       </c>
-      <c r="D9" s="6" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -42985,7 +42993,7 @@
           <t>CLUB_S1994_95_0080</t>
         </is>
       </c>
-      <c r="D10" s="6" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>TBD: auto-prev_club_id doplnění → CLUB_S1993_94_0096 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
@@ -43005,7 +43013,7 @@
           <t>CLUB_S1994_95_0107</t>
         </is>
       </c>
-      <c r="D11" s="6" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>TBD: auto-prev_club_id doplnění → CLUB_S1993_94_0124 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
@@ -43025,7 +43033,7 @@
           <t>CLUB_S1994_95_0121</t>
         </is>
       </c>
-      <c r="D12" s="6" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -43045,7 +43053,7 @@
           <t>CLUB_S1994_95_0137</t>
         </is>
       </c>
-      <c r="D13" s="6" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -43065,7 +43073,7 @@
           <t>CLUB_S1994_95_0139</t>
         </is>
       </c>
-      <c r="D14" s="6" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -43085,7 +43093,7 @@
           <t>CLUB_S1994_95_0174</t>
         </is>
       </c>
-      <c r="D15" s="6" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
@@ -43105,7 +43113,7 @@
           <t>CLUB_S1994_95_0175</t>
         </is>
       </c>
-      <c r="D16" s="6" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
         </is>
@@ -43125,7 +43133,7 @@
           <t>CLUB_S1994_95_0176</t>
         </is>
       </c>
-      <c r="D17" s="6" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>TBD: city 'Bižuterie Jablonec' → 'Jablonec nad Nisou' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
@@ -43145,7 +43153,7 @@
           <t>CLUB_S1994_95_0183</t>
         </is>
       </c>
-      <c r="D18" s="6" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
         </is>
@@ -43165,7 +43173,7 @@
           <t>CLUB_S1994_95_0184</t>
         </is>
       </c>
-      <c r="D19" s="6" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
         </is>
@@ -43185,7 +43193,7 @@
           <t>CLUB_S1994_95_0195</t>
         </is>
       </c>
-      <c r="D20" s="6" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>TBD: city 'Stadion Nový Bydžov' → 'Nový Bydžov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -43205,7 +43213,7 @@
           <t>CLUB_S1994_95_0214</t>
         </is>
       </c>
-      <c r="D21" s="6" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>TBD: K ověření, zda jde o B-tým nebo samostatný klub (Česká Třebová mohla mít dva různé kluby). Smart fix prev: 0650 (Sokol Česká Třebová = jiný klub) → 0656 (Perla II z 49/50 = B-tým Perly). Audit 04/2026.</t>
         </is>
@@ -43225,7 +43233,7 @@
           <t>CLUB_S1994_95_0222</t>
         </is>
       </c>
-      <c r="D22" s="6" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -43245,7 +43253,7 @@
           <t>CLUB_S1994_95_0237</t>
         </is>
       </c>
-      <c r="D23" s="6" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
         </is>
@@ -43265,7 +43273,7 @@
           <t>CLUB_S1994_95_0242</t>
         </is>
       </c>
-      <c r="D24" s="6" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>TBD: clean = "(Třešť) – (Dačice)" - format meziokresni soutez nejasny. K vyjasneni Pavlem (D40). Almanach komentar ponechan.</t>
         </is>
@@ -43285,7 +43293,7 @@
           <t>CLUB_S1994_95_0262</t>
         </is>
       </c>
-      <c r="D25" s="6" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>TBD: auto-prev_club_id doplnění → CLUB_S1993_94_0340 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
@@ -43305,7 +43313,7 @@
           <t>CLUB_S1994_95_0267</t>
         </is>
       </c>
-      <c r="D26" s="6" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>TBD: auto-prev_club_id doplnění → CLUB_S1993_94_0358 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
@@ -43325,7 +43333,7 @@
           <t>CLUB_S1994_95_0299</t>
         </is>
       </c>
-      <c r="D27" s="6" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t>TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -43345,11 +43353,115 @@
           <t>CLUB_S1994_95_0300</t>
         </is>
       </c>
-      <c r="D28" s="6" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="7" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" s="8" t="inlineStr">
+        <is>
+          <t>torzo</t>
+        </is>
+      </c>
+      <c r="C29" s="7" t="inlineStr">
+        <is>
+          <t>Jihomoravský – KP I.třídy (Jihomoravský kraj) · NODE_S1994_95_0090</t>
+        </is>
+      </c>
+      <c r="D29" s="7" t="inlineStr">
+        <is>
+          <t>máme jen 1 tým (Malhostovice), chybí zbytek týmů i celá tabulka  [torzo-audit]</t>
+        </is>
+      </c>
+      <c r="E29" s="7" t="inlineStr">
+        <is>
+          <t>ne</t>
+        </is>
+      </c>
+      <c r="F29" s="7" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="7" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" s="8" t="inlineStr">
+        <is>
+          <t>torzo</t>
+        </is>
+      </c>
+      <c r="C30" s="7" t="inlineStr">
+        <is>
+          <t>Severomoravský – KP I.třídy (jihozápadní Morava) · NODE_S1994_95_0092</t>
+        </is>
+      </c>
+      <c r="D30" s="7" t="inlineStr">
+        <is>
+          <t>máme jen 1 tým (Poruba), chybí zbytek týmů i celá tabulka  [torzo-audit]</t>
+        </is>
+      </c>
+      <c r="E30" s="7" t="inlineStr">
+        <is>
+          <t>ne</t>
+        </is>
+      </c>
+      <c r="F30" s="7" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" s="8" t="inlineStr">
+        <is>
+          <t>torzo</t>
+        </is>
+      </c>
+      <c r="C31" s="7" t="inlineStr">
+        <is>
+          <t>30_Jihočeský L40 O 5.-6.místo (Jihočeský kraj) · NODE_S1994_95_0045</t>
+        </is>
+      </c>
+      <c r="D31" s="7" t="inlineStr">
+        <is>
+          <t>máme jen 2 týmy (TJ Lokomotiva Veselí nad Lužnicí, HC Slavoj Rekostav Č. Krumlov), chybí zbytek týmů a tabulka  [torzo-audit]</t>
+        </is>
+      </c>
+      <c r="E31" s="7" t="inlineStr">
+        <is>
+          <t>ne</t>
+        </is>
+      </c>
+      <c r="F31" s="7" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="7" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" s="8" t="inlineStr">
+        <is>
+          <t>torzo</t>
+        </is>
+      </c>
+      <c r="C32" s="7" t="inlineStr">
+        <is>
+          <t>30_Středočeský Do II.ligy bez kvalifikace postoupila mužstva Stadion Nymburk (Středočeský kraj) · NODE_S1994_95_0040</t>
+        </is>
+      </c>
+      <c r="D32" s="7" t="inlineStr">
+        <is>
+          <t>máme jen účastníky (a Spolana Neratovice), chybí výsledek / odveta  [torzo-audit]</t>
+        </is>
+      </c>
+      <c r="E32" s="7" t="inlineStr">
+        <is>
+          <t>ne</t>
+        </is>
+      </c>
+      <c r="F32" s="7" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:F28"/>

--- a/data/S1994_95_FINAL.xlsx
+++ b/data/S1994_95_FINAL.xlsx
@@ -105,7 +105,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -119,6 +119,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -17890,7 +17893,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D29"/>
+  <dimension ref="A1:D33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18256,6 +18259,74 @@
         </is>
       </c>
       <c r="D29" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>NODE_S1994_95_0090</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>[TBD] torzo: máme jen 1 tým (Malhostovice), chybí zbytek týmů i celá tabulka  [torzo-audit]</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>NODE_S1994_95_0092</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>[TBD] torzo: máme jen 1 tým (Poruba), chybí zbytek týmů i celá tabulka  [torzo-audit]</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>NODE_S1994_95_0045</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>[TBD] torzo: máme jen 2 týmy (TJ Lokomotiva Veselí nad Lužnicí, HC Slavoj Rekostav Č. Krumlov), chybí zbytek týmů a tabulka  [torzo-audit]</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>NODE_S1994_95_0040</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>[TBD] torzo: máme jen účastníky (a Spolana Neratovice), chybí výsledek / odveta  [torzo-audit]</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
         <is>
           <t>TODO-auto</t>
         </is>
@@ -43373,7 +43444,7 @@
           <t>Jihomoravský – KP I.třídy (Jihomoravský kraj) · NODE_S1994_95_0090</t>
         </is>
       </c>
-      <c r="D29" s="7" t="inlineStr">
+      <c r="D29" s="9" t="inlineStr">
         <is>
           <t>máme jen 1 tým (Malhostovice), chybí zbytek týmů i celá tabulka  [torzo-audit]</t>
         </is>
@@ -43399,7 +43470,7 @@
           <t>Severomoravský – KP I.třídy (jihozápadní Morava) · NODE_S1994_95_0092</t>
         </is>
       </c>
-      <c r="D30" s="7" t="inlineStr">
+      <c r="D30" s="9" t="inlineStr">
         <is>
           <t>máme jen 1 tým (Poruba), chybí zbytek týmů i celá tabulka  [torzo-audit]</t>
         </is>
@@ -43425,7 +43496,7 @@
           <t>30_Jihočeský L40 O 5.-6.místo (Jihočeský kraj) · NODE_S1994_95_0045</t>
         </is>
       </c>
-      <c r="D31" s="7" t="inlineStr">
+      <c r="D31" s="9" t="inlineStr">
         <is>
           <t>máme jen 2 týmy (TJ Lokomotiva Veselí nad Lužnicí, HC Slavoj Rekostav Č. Krumlov), chybí zbytek týmů a tabulka  [torzo-audit]</t>
         </is>
@@ -43451,7 +43522,7 @@
           <t>30_Středočeský Do II.ligy bez kvalifikace postoupila mužstva Stadion Nymburk (Středočeský kraj) · NODE_S1994_95_0040</t>
         </is>
       </c>
-      <c r="D32" s="7" t="inlineStr">
+      <c r="D32" s="9" t="inlineStr">
         <is>
           <t>máme jen účastníky (a Spolana Neratovice), chybí výsledek / odveta  [torzo-audit]</t>
         </is>

--- a/data/S1994_95_FINAL.xlsx
+++ b/data/S1994_95_FINAL.xlsx
@@ -19895,7 +19895,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>30_Praha L40</t>
+          <t>Praha, 4. úroveň</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -19942,7 +19942,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>30_Praha L50</t>
+          <t>Praha, 5. úroveň</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -19984,7 +19984,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>30_Praha L50</t>
+          <t>Praha, 5. úroveň</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -20279,7 +20279,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>30_Středočeský L40</t>
+          <t>Středočeský, 4. úroveň</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -20326,7 +20326,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>30_Středočeský L50</t>
+          <t>Středočeský, 5. úroveň</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -20373,7 +20373,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>30_Středočeský L40 KP I.třídy</t>
+          <t>Středočeský, 4. úroveň KP I.třídy</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -20415,7 +20415,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>30_Středočeský L40 KP II.třídy</t>
+          <t>Středočeský, 4. úroveň KP II.třídy</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -20457,7 +20457,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>30_Středočeský Do II.ligy bez kvalifikace postoupila mužstva Stadion Nymburk</t>
+          <t>Středočeský Do II.ligy bez kvalifikace postoupila mužstva Stadion Nymburk</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -20504,7 +20504,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>30_Jihočeský L40</t>
+          <t>Jihočeský, 4. úroveň</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -20551,7 +20551,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>30_Jihočeský L50</t>
+          <t>Jihočeský, 5. úroveň</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -20598,7 +20598,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>30_Jihočeský L40 základní část</t>
+          <t>Jihočeský, 4. úroveň, základní část</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -20653,7 +20653,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>30_Jihočeský L40 nadstavba</t>
+          <t>Jihočeský, 4. úroveň nadstavba</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -20695,7 +20695,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>30_Jihočeský L40 O 5.-6.místo</t>
+          <t>Jihočeský, 4. úroveň O 5.-6.místo</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -20745,7 +20745,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>30_Jihočeský L40 KS</t>
+          <t>Jihočeský, 4. úroveň KS</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -20787,7 +20787,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>30_Západočeský L40</t>
+          <t>Západočeský, 4. úroveň</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -20834,7 +20834,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>30_Západočeský L50</t>
+          <t>Západočeský, 5. úroveň</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -20881,7 +20881,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>30_Západočeský L40 KP I.třídy</t>
+          <t>Západočeský, 4. úroveň KP I.třídy</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -20923,7 +20923,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>30_Západočeský L40 základní část</t>
+          <t>Západočeský, 4. úroveň, základní část</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -20965,7 +20965,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>30_Západočeský L40 nadstavba</t>
+          <t>Západočeský, 4. úroveň nadstavba</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -21007,7 +21007,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>30_Západočeský L40 KP II.třídy</t>
+          <t>Západočeský, 4. úroveň KP II.třídy</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -21049,7 +21049,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>30_Severočeský L40</t>
+          <t>Severočeský, 4. úroveň</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -21096,7 +21096,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>30_Severočeský L50</t>
+          <t>Severočeský, 5. úroveň</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -21143,7 +21143,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>30_Východočeský L40</t>
+          <t>Východočeský, 4. úroveň</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -21190,7 +21190,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>30_Východočeský L50</t>
+          <t>Východočeský, 5. úroveň</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -21237,7 +21237,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>30_Východočeský L40 KP I.třídy</t>
+          <t>Východočeský, 4. úroveň KP I.třídy</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -21279,7 +21279,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>30_Východočeský L40 Základní část</t>
+          <t>Východočeský, 4. úroveň, Základní část</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -21339,7 +21339,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>30_Východočeský L40 finálová skupina</t>
+          <t>Východočeský, 4. úroveň finálová skupina</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -21386,7 +21386,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>30_Východočeský L40 skupina o 5.-10. místo</t>
+          <t>Východočeský, 4. úroveň, skupina o 5.-10. místo</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -21436,7 +21436,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>30_Východočeský L40 KS</t>
+          <t>Východočeský, 4. úroveň KS</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -21478,7 +21478,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>30_Východočeský L40 skupina Sever</t>
+          <t>Východočeský, 4. úroveň, skupina Sever</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -21520,7 +21520,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>30_Východočeský L40 skupina Jih</t>
+          <t>Východočeský, 4. úroveň, skupina Jih</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -21562,7 +21562,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>30_Východočeský L40 finále</t>
+          <t>Východočeský, 4. úroveň, finále</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -21612,7 +21612,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>30_Jihomoravský L40</t>
+          <t>Jihomoravský, 4. úroveň</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -21659,7 +21659,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>30_Jihomoravský L50</t>
+          <t>Jihomoravský, 5. úroveň</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -21706,7 +21706,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>30_Jihomoravský L40 KP I.třídy</t>
+          <t>Jihomoravský, 4. úroveň KP I.třídy</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -21748,7 +21748,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>30_Jihomoravský L40 KP II.třídy</t>
+          <t>Jihomoravský, 4. úroveň KP II.třídy</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -21790,7 +21790,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>30_Jihomoravský L40 skupina A</t>
+          <t>Jihomoravský, 4. úroveň, skupina A</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -21837,7 +21837,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>30_Jihomoravský L40 skupina B</t>
+          <t>Jihomoravský, 4. úroveň, skupina B</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -21884,7 +21884,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>30_Jihomoravský L40 skupina C</t>
+          <t>Jihomoravský, 4. úroveň, skupina C</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -21931,7 +21931,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>30_Jihomoravský L40 skupina D</t>
+          <t>Jihomoravský, 4. úroveň, skupina D</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -21978,7 +21978,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>30_Jihomoravský L40 finálová skupina A + B</t>
+          <t>Jihomoravský, 4. úroveň finálová skupina A + B</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -22020,7 +22020,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>30_Jihomoravský L40 finálová skupina C+ D</t>
+          <t>Jihomoravský, 4. úroveň finálová skupina C+ D</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -22062,7 +22062,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>30_Jihomoravský L40 o udržení A</t>
+          <t>Jihomoravský, 4. úroveň o udržení A</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -22117,7 +22117,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>30_Jihomoravský L40 o udržení B</t>
+          <t>Jihomoravský, 4. úroveň o udržení B</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -22172,7 +22172,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>30_Jihomoravský L40 o udržení C</t>
+          <t>Jihomoravský, 4. úroveň o udržení C</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -22227,7 +22227,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>30_Jihomoravský L40 o udržení D</t>
+          <t>Jihomoravský, 4. úroveň o udržení D</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -22282,7 +22282,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>30_Severomoravský L40</t>
+          <t>Severomoravský, 4. úroveň</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -22329,7 +22329,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>30_Severomoravský L50</t>
+          <t>Severomoravský, 5. úroveň</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -22376,7 +22376,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>30_Severomoravský L40 KP I.třídy</t>
+          <t>Severomoravský, 4. úroveň KP I.třídy</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -22418,7 +22418,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>30_Severomoravský L40 KP II.třídy</t>
+          <t>Severomoravský, 4. úroveň KP II.třídy</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -22460,7 +22460,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>30_Severomoravský L40 skupina A</t>
+          <t>Severomoravský, 4. úroveň, skupina A</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -22507,7 +22507,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>30_Severomoravský L40 skupina B</t>
+          <t>Severomoravský, 4. úroveň, skupina B</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -22554,7 +22554,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>30_Severomoravský L40 finálová skupina</t>
+          <t>Severomoravský, 4. úroveň finálová skupina</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -22601,7 +22601,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>30_Severomoravský L40 skupina o 7.-11.místo</t>
+          <t>Severomoravský, 4. úroveň, skupina o 7.-11.místo</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -22643,6 +22643,8 @@
         <v>5</v>
       </c>
     </row>
+    <row r="88"/>
+    <row r="89"/>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
@@ -22675,7 +22677,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>I.ČNHL (12 CZ) + SNHL (12 SVK)</t>
+          <t>I.ČNHL (12 CZ) + SNHL (12 Slovensko)</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -22772,6 +22774,7 @@
         </is>
       </c>
     </row>
+    <row r="97"/>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>

--- a/data/S1994_95_FINAL.xlsx
+++ b/data/S1994_95_FINAL.xlsx
@@ -825,7 +825,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -903,7 +903,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -981,7 +981,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1059,7 +1059,7 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1137,7 +1137,7 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1215,7 +1215,7 @@
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -1376,7 +1376,7 @@
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
@@ -1454,7 +1454,7 @@
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>o udržení</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
@@ -1532,7 +1532,7 @@
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>o udržení</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
@@ -1610,7 +1610,7 @@
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>o udržení</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
@@ -1688,7 +1688,7 @@
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>o udržení</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
@@ -2207,7 +2207,7 @@
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>udržel se</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
@@ -2285,7 +2285,7 @@
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>udržel se</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
@@ -2363,7 +2363,7 @@
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>udržel se</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
@@ -2441,7 +2441,7 @@
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>udržel se</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
@@ -2753,7 +2753,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -3070,7 +3070,7 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -3148,7 +3148,7 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -3309,7 +3309,7 @@
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -3392,7 +3392,7 @@
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>setrval?</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
@@ -3470,7 +3470,7 @@
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
@@ -22643,8 +22643,6 @@
         <v>5</v>
       </c>
     </row>
-    <row r="88"/>
-    <row r="89"/>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
@@ -22774,7 +22772,6 @@
         </is>
       </c>
     </row>
-    <row r="97"/>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
@@ -43841,7 +43838,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>postup</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -43919,7 +43916,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>postup</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -44002,7 +43999,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -44080,7 +44077,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -44158,7 +44155,7 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>zanik</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -44236,7 +44233,7 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -44314,7 +44311,7 @@
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>postup</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -44397,7 +44394,7 @@
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -44475,7 +44472,7 @@
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
@@ -44553,7 +44550,7 @@
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
@@ -44636,7 +44633,7 @@
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
@@ -44714,7 +44711,7 @@
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
@@ -44792,7 +44789,7 @@
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
@@ -44870,7 +44867,7 @@
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>sestup</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
